--- a/relatorio_grao_por_vendedor.xlsx
+++ b/relatorio_grao_por_vendedor.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G501"/>
+  <dimension ref="A1:I501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -458,8 +458,10 @@
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,12 +492,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Qtd Total</t>
+          <t>Qtd Total (cx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Média Mensal</t>
+          <t>Qtd Total (kg)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Média Mensal (cx)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Média Mensal (kg)</t>
         </is>
       </c>
     </row>
@@ -525,7 +537,13 @@
         <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>4</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -554,7 +572,13 @@
         <v>88</v>
       </c>
       <c r="G3" s="4" t="n">
+        <v>528</v>
+      </c>
+      <c r="H3" s="4" t="n">
         <v>44</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="4">
@@ -583,7 +607,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -612,7 +642,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -628,7 +664,11 @@
       <c r="F6" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="G6" s="6" t="n"/>
+      <c r="G6" s="7" t="n">
+        <v>564</v>
+      </c>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -656,7 +696,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -685,7 +731,13 @@
         <v>46</v>
       </c>
       <c r="G8" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>3.8</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>22.8</v>
       </c>
     </row>
     <row r="9">
@@ -714,7 +766,13 @@
         <v>2</v>
       </c>
       <c r="G9" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -743,7 +801,13 @@
         <v>21</v>
       </c>
       <c r="G10" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>3.5</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -772,7 +836,13 @@
         <v>11</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>1.1</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="12">
@@ -801,7 +871,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -830,7 +906,13 @@
         <v>25</v>
       </c>
       <c r="G13" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>2.1</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>12.6</v>
       </c>
     </row>
     <row r="14">
@@ -859,7 +941,13 @@
         <v>12</v>
       </c>
       <c r="G14" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -888,7 +976,13 @@
         <v>16</v>
       </c>
       <c r="G15" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="16">
@@ -917,7 +1011,13 @@
         <v>7</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="17">
@@ -946,7 +1046,13 @@
         <v>47</v>
       </c>
       <c r="G17" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="H17" s="4" t="n">
         <v>3.9</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>23.4</v>
       </c>
     </row>
     <row r="18">
@@ -975,7 +1081,13 @@
         <v>22</v>
       </c>
       <c r="G18" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="H18" s="4" t="n">
         <v>3.7</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>22.2</v>
       </c>
     </row>
     <row r="19">
@@ -1004,7 +1116,13 @@
         <v>14</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="20">
@@ -1033,7 +1151,13 @@
         <v>7</v>
       </c>
       <c r="G20" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H20" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="21">
@@ -1062,7 +1186,13 @@
         <v>12</v>
       </c>
       <c r="G21" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H21" s="4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="22">
@@ -1091,7 +1221,13 @@
         <v>6</v>
       </c>
       <c r="G22" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="H22" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1120,7 +1256,13 @@
         <v>21</v>
       </c>
       <c r="G23" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="H23" s="3" t="n">
         <v>1.9</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>11.4</v>
       </c>
     </row>
     <row r="24">
@@ -1149,7 +1291,13 @@
         <v>10</v>
       </c>
       <c r="G24" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="25">
@@ -1178,7 +1326,13 @@
         <v>18</v>
       </c>
       <c r="G25" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="H25" s="4" t="n">
         <v>1.5</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1207,7 +1361,13 @@
         <v>8</v>
       </c>
       <c r="G26" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H26" s="4" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="27">
@@ -1236,7 +1396,13 @@
         <v>11</v>
       </c>
       <c r="G27" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="H27" s="3" t="n">
         <v>1.1</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="28">
@@ -1265,7 +1431,13 @@
         <v>4</v>
       </c>
       <c r="G28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -1294,7 +1466,13 @@
         <v>17</v>
       </c>
       <c r="G29" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="H29" s="4" t="n">
         <v>2.4</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>14.4</v>
       </c>
     </row>
     <row r="30">
@@ -1323,7 +1501,13 @@
         <v>31</v>
       </c>
       <c r="G30" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="H30" s="3" t="n">
         <v>2.6</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>15.6</v>
       </c>
     </row>
     <row r="31">
@@ -1352,7 +1536,13 @@
         <v>10</v>
       </c>
       <c r="G31" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1381,7 +1571,13 @@
         <v>2</v>
       </c>
       <c r="G32" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -1410,7 +1606,13 @@
         <v>30</v>
       </c>
       <c r="G33" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>5</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="34">
@@ -1439,7 +1641,13 @@
         <v>21</v>
       </c>
       <c r="G34" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="H34" s="4" t="n">
         <v>3.5</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="35">
@@ -1468,7 +1676,13 @@
         <v>28</v>
       </c>
       <c r="G35" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="H35" s="4" t="n">
         <v>4</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="36">
@@ -1497,7 +1711,13 @@
         <v>68</v>
       </c>
       <c r="G36" s="3" t="n">
+        <v>408</v>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>5.7</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="37">
@@ -1526,7 +1746,13 @@
         <v>32</v>
       </c>
       <c r="G37" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="H37" s="3" t="n">
         <v>5.3</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="38">
@@ -1555,7 +1781,13 @@
         <v>14</v>
       </c>
       <c r="G38" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H38" s="4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="39">
@@ -1584,7 +1816,13 @@
         <v>7</v>
       </c>
       <c r="G39" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="40">
@@ -1613,7 +1851,13 @@
         <v>32</v>
       </c>
       <c r="G40" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="41">
@@ -1642,7 +1886,13 @@
         <v>14</v>
       </c>
       <c r="G41" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H41" s="3" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="42">
@@ -1671,7 +1921,13 @@
         <v>51</v>
       </c>
       <c r="G42" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="H42" s="4" t="n">
         <v>6.4</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>38.4</v>
       </c>
     </row>
     <row r="43">
@@ -1700,7 +1956,13 @@
         <v>25</v>
       </c>
       <c r="G43" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H43" s="4" t="n">
         <v>5</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -1729,7 +1991,13 @@
         <v>50</v>
       </c>
       <c r="G44" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>5</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="45">
@@ -1758,7 +2026,13 @@
         <v>20</v>
       </c>
       <c r="G45" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>4</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="46">
@@ -1787,7 +2061,13 @@
         <v>40</v>
       </c>
       <c r="G46" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="H46" s="4" t="n">
         <v>3.3</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>19.8</v>
       </c>
     </row>
     <row r="47">
@@ -1816,7 +2096,13 @@
         <v>14</v>
       </c>
       <c r="G47" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H47" s="4" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="48">
@@ -1845,7 +2131,13 @@
         <v>120</v>
       </c>
       <c r="G48" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="H48" s="3" t="n">
         <v>10</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="49">
@@ -1874,7 +2166,13 @@
         <v>57</v>
       </c>
       <c r="G49" s="3" t="n">
+        <v>342</v>
+      </c>
+      <c r="H49" s="3" t="n">
         <v>9.5</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="50">
@@ -1903,7 +2201,13 @@
         <v>61</v>
       </c>
       <c r="G50" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="H50" s="4" t="n">
         <v>6.8</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>40.8</v>
       </c>
     </row>
     <row r="51">
@@ -1932,7 +2236,13 @@
         <v>23</v>
       </c>
       <c r="G51" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="H51" s="4" t="n">
         <v>3.8</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>22.8</v>
       </c>
     </row>
     <row r="52">
@@ -1961,7 +2271,13 @@
         <v>47</v>
       </c>
       <c r="G52" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="H52" s="3" t="n">
         <v>3.9</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>23.4</v>
       </c>
     </row>
     <row r="53">
@@ -1990,7 +2306,13 @@
         <v>24</v>
       </c>
       <c r="G53" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="H53" s="3" t="n">
         <v>4</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="54">
@@ -2019,7 +2341,13 @@
         <v>14</v>
       </c>
       <c r="G54" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H54" s="4" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="55">
@@ -2048,7 +2376,13 @@
         <v>8</v>
       </c>
       <c r="G55" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H55" s="4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="56">
@@ -2077,7 +2411,13 @@
         <v>213</v>
       </c>
       <c r="G56" s="3" t="n">
+        <v>1278</v>
+      </c>
+      <c r="H56" s="3" t="n">
         <v>21.3</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>127.8</v>
       </c>
     </row>
     <row r="57">
@@ -2106,7 +2446,13 @@
         <v>85</v>
       </c>
       <c r="G57" s="3" t="n">
+        <v>510</v>
+      </c>
+      <c r="H57" s="3" t="n">
         <v>21.2</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>127.2</v>
       </c>
     </row>
     <row r="58">
@@ -2135,7 +2481,13 @@
         <v>1</v>
       </c>
       <c r="G58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -2164,7 +2516,13 @@
         <v>55</v>
       </c>
       <c r="G59" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="H59" s="3" t="n">
         <v>4.6</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>27.6</v>
       </c>
     </row>
     <row r="60">
@@ -2193,7 +2551,13 @@
         <v>29</v>
       </c>
       <c r="G60" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="H60" s="3" t="n">
         <v>4.8</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>28.8</v>
       </c>
     </row>
     <row r="61">
@@ -2222,7 +2586,13 @@
         <v>20</v>
       </c>
       <c r="G61" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H61" s="4" t="n">
         <v>4</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="62">
@@ -2251,7 +2621,13 @@
         <v>15</v>
       </c>
       <c r="G62" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="H62" s="4" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="63">
@@ -2280,7 +2656,13 @@
         <v>62</v>
       </c>
       <c r="G63" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="H63" s="3" t="n">
         <v>6.2</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>37.2</v>
       </c>
     </row>
     <row r="64">
@@ -2309,7 +2691,13 @@
         <v>9</v>
       </c>
       <c r="G64" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H64" s="4" t="n">
         <v>1.1</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="65">
@@ -2338,7 +2726,13 @@
         <v>2</v>
       </c>
       <c r="G65" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H65" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -2367,7 +2761,13 @@
         <v>2</v>
       </c>
       <c r="G66" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H66" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -2396,7 +2796,13 @@
         <v>4</v>
       </c>
       <c r="G67" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H67" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -2425,7 +2831,13 @@
         <v>70</v>
       </c>
       <c r="G68" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="H68" s="4" t="n">
         <v>35</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="69">
@@ -2454,7 +2866,13 @@
         <v>33</v>
       </c>
       <c r="G69" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="H69" s="4" t="n">
         <v>5.5</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="70">
@@ -2470,7 +2888,11 @@
       <c r="F70" s="7" t="n">
         <v>1782</v>
       </c>
-      <c r="G70" s="6" t="n"/>
+      <c r="G70" s="7" t="n">
+        <v>10692</v>
+      </c>
+      <c r="H70" s="6" t="n"/>
+      <c r="I70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2498,7 +2920,13 @@
         <v>30</v>
       </c>
       <c r="G71" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="H71" s="3" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="72">
@@ -2527,7 +2955,13 @@
         <v>14</v>
       </c>
       <c r="G72" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H72" s="3" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="73">
@@ -2556,7 +2990,13 @@
         <v>4</v>
       </c>
       <c r="G73" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H73" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -2585,7 +3025,13 @@
         <v>2</v>
       </c>
       <c r="G74" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H74" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -2614,7 +3060,13 @@
         <v>30</v>
       </c>
       <c r="G75" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="H75" s="3" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="76">
@@ -2643,7 +3095,13 @@
         <v>15</v>
       </c>
       <c r="G76" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H76" s="3" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -2672,7 +3130,13 @@
         <v>11</v>
       </c>
       <c r="G77" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="H77" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -2701,7 +3165,13 @@
         <v>5</v>
       </c>
       <c r="G78" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H78" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -2730,7 +3200,13 @@
         <v>8</v>
       </c>
       <c r="G79" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H79" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -2759,7 +3235,13 @@
         <v>2</v>
       </c>
       <c r="G80" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H80" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -2788,7 +3270,13 @@
         <v>25</v>
       </c>
       <c r="G81" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H81" s="4" t="n">
         <v>2.1</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>12.6</v>
       </c>
     </row>
     <row r="82">
@@ -2817,7 +3305,13 @@
         <v>13</v>
       </c>
       <c r="G82" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="H82" s="4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="83">
@@ -2846,7 +3340,13 @@
         <v>23</v>
       </c>
       <c r="G83" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="H83" s="3" t="n">
         <v>1.9</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>11.4</v>
       </c>
     </row>
     <row r="84">
@@ -2875,7 +3375,13 @@
         <v>9</v>
       </c>
       <c r="G84" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H84" s="3" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="85">
@@ -2904,7 +3410,13 @@
         <v>8</v>
       </c>
       <c r="G85" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H85" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -2933,7 +3445,13 @@
         <v>4</v>
       </c>
       <c r="G86" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H86" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="87">
@@ -2962,7 +3480,13 @@
         <v>8</v>
       </c>
       <c r="G87" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H87" s="3" t="n">
         <v>1.1</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="88">
@@ -2991,7 +3515,13 @@
         <v>4</v>
       </c>
       <c r="G88" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H88" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -3020,7 +3550,13 @@
         <v>27</v>
       </c>
       <c r="G89" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="H89" s="4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="90">
@@ -3049,7 +3585,13 @@
         <v>11</v>
       </c>
       <c r="G90" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="H90" s="4" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="91">
@@ -3078,7 +3620,13 @@
         <v>22</v>
       </c>
       <c r="G91" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="H91" s="3" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="92">
@@ -3107,7 +3655,13 @@
         <v>10</v>
       </c>
       <c r="G92" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H92" s="3" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="93">
@@ -3136,7 +3690,13 @@
         <v>7</v>
       </c>
       <c r="G93" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H93" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="94">
@@ -3165,7 +3725,13 @@
         <v>3</v>
       </c>
       <c r="G94" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H94" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -3194,7 +3760,13 @@
         <v>9</v>
       </c>
       <c r="G95" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H95" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="96">
@@ -3223,7 +3795,13 @@
         <v>5</v>
       </c>
       <c r="G96" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H96" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="97">
@@ -3252,7 +3830,13 @@
         <v>29</v>
       </c>
       <c r="G97" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>2.4</v>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>14.4</v>
       </c>
     </row>
     <row r="98">
@@ -3281,7 +3865,13 @@
         <v>12</v>
       </c>
       <c r="G98" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>2.4</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>14.4</v>
       </c>
     </row>
     <row r="99">
@@ -3310,7 +3900,13 @@
         <v>12</v>
       </c>
       <c r="G99" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H99" s="3" t="n">
         <v>1.1</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="100">
@@ -3339,7 +3935,13 @@
         <v>6</v>
       </c>
       <c r="G100" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H100" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="101">
@@ -3368,7 +3970,13 @@
         <v>42</v>
       </c>
       <c r="G101" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="H101" s="4" t="n">
         <v>3.5</v>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="102">
@@ -3397,7 +4005,13 @@
         <v>18</v>
       </c>
       <c r="G102" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="H102" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="103">
@@ -3426,7 +4040,13 @@
         <v>19</v>
       </c>
       <c r="G103" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="H103" s="3" t="n">
         <v>1.9</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>11.4</v>
       </c>
     </row>
     <row r="104">
@@ -3455,7 +4075,13 @@
         <v>6</v>
       </c>
       <c r="G104" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H104" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="105">
@@ -3484,7 +4110,13 @@
         <v>11</v>
       </c>
       <c r="G105" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="H105" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I105" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="106">
@@ -3513,7 +4145,13 @@
         <v>3</v>
       </c>
       <c r="G106" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H106" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="107">
@@ -3542,7 +4180,13 @@
         <v>28</v>
       </c>
       <c r="G107" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="H107" s="3" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="108">
@@ -3571,7 +4215,13 @@
         <v>12</v>
       </c>
       <c r="G108" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H108" s="3" t="n">
         <v>2.4</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>14.4</v>
       </c>
     </row>
     <row r="109">
@@ -3600,7 +4250,13 @@
         <v>3</v>
       </c>
       <c r="G109" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H109" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I109" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="110">
@@ -3629,7 +4285,13 @@
         <v>1</v>
       </c>
       <c r="G110" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H110" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I110" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -3658,7 +4320,13 @@
         <v>44</v>
       </c>
       <c r="G111" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="H111" s="3" t="n">
         <v>3.7</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>22.2</v>
       </c>
     </row>
     <row r="112">
@@ -3687,7 +4355,13 @@
         <v>39</v>
       </c>
       <c r="G112" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="H112" s="3" t="n">
         <v>7.8</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>46.8</v>
       </c>
     </row>
     <row r="113">
@@ -3716,7 +4390,13 @@
         <v>68</v>
       </c>
       <c r="G113" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="H113" s="4" t="n">
         <v>5.7</v>
+      </c>
+      <c r="I113" s="4" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="114">
@@ -3745,7 +4425,13 @@
         <v>1</v>
       </c>
       <c r="G114" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H114" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I114" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="115">
@@ -3774,7 +4460,13 @@
         <v>5</v>
       </c>
       <c r="G115" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H115" s="3" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="116">
@@ -3803,7 +4495,13 @@
         <v>42</v>
       </c>
       <c r="G116" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="H116" s="4" t="n">
         <v>3.8</v>
+      </c>
+      <c r="I116" s="4" t="n">
+        <v>22.8</v>
       </c>
     </row>
     <row r="117">
@@ -3832,7 +4530,13 @@
         <v>22</v>
       </c>
       <c r="G117" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="H117" s="4" t="n">
         <v>3.7</v>
+      </c>
+      <c r="I117" s="4" t="n">
+        <v>22.2</v>
       </c>
     </row>
     <row r="118">
@@ -3861,7 +4565,13 @@
         <v>64</v>
       </c>
       <c r="G118" s="3" t="n">
+        <v>384</v>
+      </c>
+      <c r="H118" s="3" t="n">
         <v>5.3</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="119">
@@ -3890,7 +4600,13 @@
         <v>31</v>
       </c>
       <c r="G119" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="H119" s="3" t="n">
         <v>5.2</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>31.2</v>
       </c>
     </row>
     <row r="120">
@@ -3919,7 +4635,13 @@
         <v>3</v>
       </c>
       <c r="G120" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H120" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I120" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="121">
@@ -3948,7 +4670,13 @@
         <v>23</v>
       </c>
       <c r="G121" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="H121" s="3" t="n">
         <v>1.9</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>11.4</v>
       </c>
     </row>
     <row r="122">
@@ -3977,7 +4705,13 @@
         <v>11</v>
       </c>
       <c r="G122" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="H122" s="3" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="123">
@@ -4006,7 +4740,13 @@
         <v>91</v>
       </c>
       <c r="G123" s="4" t="n">
+        <v>546</v>
+      </c>
+      <c r="H123" s="4" t="n">
         <v>7.6</v>
+      </c>
+      <c r="I123" s="4" t="n">
+        <v>45.6</v>
       </c>
     </row>
     <row r="124">
@@ -4035,7 +4775,13 @@
         <v>43</v>
       </c>
       <c r="G124" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="H124" s="4" t="n">
         <v>7.2</v>
+      </c>
+      <c r="I124" s="4" t="n">
+        <v>43.2</v>
       </c>
     </row>
     <row r="125">
@@ -4064,7 +4810,13 @@
         <v>15</v>
       </c>
       <c r="G125" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H125" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="126">
@@ -4093,7 +4845,13 @@
         <v>7</v>
       </c>
       <c r="G126" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H126" s="3" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="127">
@@ -4122,7 +4880,13 @@
         <v>9</v>
       </c>
       <c r="G127" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H127" s="4" t="n">
         <v>4.5</v>
+      </c>
+      <c r="I127" s="4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="128">
@@ -4151,7 +4915,13 @@
         <v>15</v>
       </c>
       <c r="G128" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="H128" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="I128" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="129">
@@ -4180,7 +4950,13 @@
         <v>25</v>
       </c>
       <c r="G129" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H129" s="3" t="n">
         <v>4.2</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>25.2</v>
       </c>
     </row>
     <row r="130">
@@ -4209,7 +4985,13 @@
         <v>2</v>
       </c>
       <c r="G130" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H130" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I130" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="131">
@@ -4238,7 +5020,13 @@
         <v>3</v>
       </c>
       <c r="G131" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H131" s="3" t="n">
         <v>3</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="132">
@@ -4267,7 +5055,13 @@
         <v>16</v>
       </c>
       <c r="G132" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H132" s="4" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I132" s="4" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="133">
@@ -4296,7 +5090,13 @@
         <v>76</v>
       </c>
       <c r="G133" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="H133" s="3" t="n">
         <v>6.3</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>37.8</v>
       </c>
     </row>
     <row r="134">
@@ -4325,7 +5125,13 @@
         <v>30</v>
       </c>
       <c r="G134" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="H134" s="3" t="n">
         <v>5</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="135">
@@ -4354,7 +5160,13 @@
         <v>33</v>
       </c>
       <c r="G135" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="H135" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="I135" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="136">
@@ -4383,7 +5195,13 @@
         <v>18</v>
       </c>
       <c r="G136" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="H136" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="I136" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="137">
@@ -4412,7 +5230,13 @@
         <v>22</v>
       </c>
       <c r="G137" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="H137" s="3" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="138">
@@ -4441,7 +5265,13 @@
         <v>10</v>
       </c>
       <c r="G138" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H138" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="139">
@@ -4470,7 +5300,13 @@
         <v>9</v>
       </c>
       <c r="G139" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H139" s="4" t="n">
         <v>1.1</v>
+      </c>
+      <c r="I139" s="4" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="140">
@@ -4499,7 +5335,13 @@
         <v>4</v>
       </c>
       <c r="G140" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H140" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I140" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="141">
@@ -4528,7 +5370,13 @@
         <v>5</v>
       </c>
       <c r="G141" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H141" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="142">
@@ -4557,7 +5405,13 @@
         <v>2</v>
       </c>
       <c r="G142" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H142" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I142" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="143">
@@ -4586,7 +5440,13 @@
         <v>1</v>
       </c>
       <c r="G143" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H143" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I143" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="144">
@@ -4615,7 +5475,13 @@
         <v>8</v>
       </c>
       <c r="G144" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H144" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I144" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="145">
@@ -4644,7 +5510,13 @@
         <v>3</v>
       </c>
       <c r="G145" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H145" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="146">
@@ -4673,7 +5545,13 @@
         <v>9</v>
       </c>
       <c r="G146" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H146" s="4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I146" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="147">
@@ -4702,7 +5580,13 @@
         <v>8</v>
       </c>
       <c r="G147" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H147" s="4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I147" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="148">
@@ -4731,7 +5615,13 @@
         <v>1</v>
       </c>
       <c r="G148" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H148" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="149">
@@ -4760,7 +5650,13 @@
         <v>7</v>
       </c>
       <c r="G149" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H149" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I149" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="150">
@@ -4789,7 +5685,13 @@
         <v>4</v>
       </c>
       <c r="G150" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H150" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I150" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="151">
@@ -4818,7 +5720,13 @@
         <v>2</v>
       </c>
       <c r="G151" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H151" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="152">
@@ -4847,7 +5755,13 @@
         <v>5</v>
       </c>
       <c r="G152" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H152" s="4" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I152" s="4" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="153">
@@ -4863,7 +5777,11 @@
       <c r="F153" s="7" t="n">
         <v>1347</v>
       </c>
-      <c r="G153" s="6" t="n"/>
+      <c r="G153" s="7" t="n">
+        <v>8082</v>
+      </c>
+      <c r="H153" s="6" t="n"/>
+      <c r="I153" s="6" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -4891,7 +5809,13 @@
         <v>1</v>
       </c>
       <c r="G154" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H154" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="155">
@@ -4920,7 +5844,13 @@
         <v>4</v>
       </c>
       <c r="G155" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H155" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I155" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="156">
@@ -4949,7 +5879,13 @@
         <v>3</v>
       </c>
       <c r="G156" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H156" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="157">
@@ -4978,7 +5914,13 @@
         <v>4</v>
       </c>
       <c r="G157" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H157" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="158">
@@ -5007,7 +5949,13 @@
         <v>1</v>
       </c>
       <c r="G158" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H158" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="159">
@@ -5036,7 +5984,13 @@
         <v>8</v>
       </c>
       <c r="G159" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H159" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="160">
@@ -5065,7 +6019,13 @@
         <v>3</v>
       </c>
       <c r="G160" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H160" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="161">
@@ -5094,7 +6054,13 @@
         <v>2</v>
       </c>
       <c r="G161" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H161" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="162">
@@ -5123,7 +6089,13 @@
         <v>4</v>
       </c>
       <c r="G162" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H162" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I162" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="163">
@@ -5152,7 +6124,13 @@
         <v>2</v>
       </c>
       <c r="G163" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H163" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I163" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="164">
@@ -5181,7 +6159,13 @@
         <v>22</v>
       </c>
       <c r="G164" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="H164" s="3" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="165">
@@ -5210,7 +6194,13 @@
         <v>11</v>
       </c>
       <c r="G165" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="H165" s="3" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="166">
@@ -5239,7 +6229,13 @@
         <v>4</v>
       </c>
       <c r="G166" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H166" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I166" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="167">
@@ -5268,7 +6264,13 @@
         <v>2</v>
       </c>
       <c r="G167" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H167" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I167" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="168">
@@ -5297,7 +6299,13 @@
         <v>13</v>
       </c>
       <c r="G168" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="H168" s="3" t="n">
         <v>1.1</v>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="169">
@@ -5326,7 +6334,13 @@
         <v>4</v>
       </c>
       <c r="G169" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H169" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="170">
@@ -5355,7 +6369,13 @@
         <v>5</v>
       </c>
       <c r="G170" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H170" s="4" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I170" s="4" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="171">
@@ -5384,7 +6404,13 @@
         <v>3</v>
       </c>
       <c r="G171" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H171" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I171" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="172">
@@ -5413,7 +6439,13 @@
         <v>36</v>
       </c>
       <c r="G172" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="H172" s="3" t="n">
         <v>3</v>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="173">
@@ -5442,7 +6474,13 @@
         <v>13</v>
       </c>
       <c r="G173" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="H173" s="3" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="174">
@@ -5471,7 +6509,13 @@
         <v>9</v>
       </c>
       <c r="G174" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H174" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="175">
@@ -5500,7 +6544,13 @@
         <v>3</v>
       </c>
       <c r="G175" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H175" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I175" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="176">
@@ -5529,7 +6579,13 @@
         <v>78</v>
       </c>
       <c r="G176" s="3" t="n">
+        <v>468</v>
+      </c>
+      <c r="H176" s="3" t="n">
         <v>6.5</v>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="177">
@@ -5558,7 +6614,13 @@
         <v>31</v>
       </c>
       <c r="G177" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="H177" s="3" t="n">
         <v>5.2</v>
+      </c>
+      <c r="I177" s="3" t="n">
+        <v>31.2</v>
       </c>
     </row>
     <row r="178">
@@ -5587,7 +6649,13 @@
         <v>28</v>
       </c>
       <c r="G178" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="H178" s="4" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I178" s="4" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="179">
@@ -5616,7 +6684,13 @@
         <v>13</v>
       </c>
       <c r="G179" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="H179" s="4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I179" s="4" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="180">
@@ -5645,7 +6719,13 @@
         <v>17</v>
       </c>
       <c r="G180" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H180" s="3" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="181">
@@ -5674,7 +6754,13 @@
         <v>5</v>
       </c>
       <c r="G181" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H181" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I181" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="182">
@@ -5703,7 +6789,13 @@
         <v>26</v>
       </c>
       <c r="G182" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="H182" s="4" t="n">
         <v>2.6</v>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>15.6</v>
       </c>
     </row>
     <row r="183">
@@ -5732,7 +6824,13 @@
         <v>9</v>
       </c>
       <c r="G183" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H183" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="I183" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="184">
@@ -5761,7 +6859,13 @@
         <v>39</v>
       </c>
       <c r="G184" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="H184" s="3" t="n">
         <v>3.2</v>
+      </c>
+      <c r="I184" s="3" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="185">
@@ -5790,7 +6894,13 @@
         <v>18</v>
       </c>
       <c r="G185" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="H185" s="3" t="n">
         <v>3</v>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="186">
@@ -5819,7 +6929,13 @@
         <v>38</v>
       </c>
       <c r="G186" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="H186" s="4" t="n">
         <v>3.2</v>
+      </c>
+      <c r="I186" s="4" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="187">
@@ -5848,7 +6964,13 @@
         <v>14</v>
       </c>
       <c r="G187" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H187" s="4" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I187" s="4" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="188">
@@ -5877,7 +6999,13 @@
         <v>15</v>
       </c>
       <c r="G188" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H188" s="3" t="n">
         <v>1.5</v>
+      </c>
+      <c r="I188" s="3" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="189">
@@ -5906,7 +7034,13 @@
         <v>4</v>
       </c>
       <c r="G189" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H189" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I189" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="190">
@@ -5935,7 +7069,13 @@
         <v>10</v>
       </c>
       <c r="G190" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H190" s="4" t="n">
         <v>3.3</v>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>19.8</v>
       </c>
     </row>
     <row r="191">
@@ -5964,7 +7104,13 @@
         <v>4</v>
       </c>
       <c r="G191" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H191" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I191" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="192">
@@ -5993,7 +7139,13 @@
         <v>10</v>
       </c>
       <c r="G192" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H192" s="4" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I192" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="193">
@@ -6022,7 +7174,13 @@
         <v>11</v>
       </c>
       <c r="G193" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="H193" s="3" t="n">
         <v>1.1</v>
+      </c>
+      <c r="I193" s="3" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="194">
@@ -6051,7 +7209,13 @@
         <v>4</v>
       </c>
       <c r="G194" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H194" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I194" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="195">
@@ -6080,7 +7244,13 @@
         <v>1</v>
       </c>
       <c r="G195" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H195" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I195" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="196">
@@ -6109,7 +7279,13 @@
         <v>5</v>
       </c>
       <c r="G196" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H196" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I196" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="197">
@@ -6138,7 +7314,13 @@
         <v>39</v>
       </c>
       <c r="G197" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="H197" s="3" t="n">
         <v>3.2</v>
+      </c>
+      <c r="I197" s="3" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="198">
@@ -6167,7 +7349,13 @@
         <v>16</v>
       </c>
       <c r="G198" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H198" s="3" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I198" s="3" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="199">
@@ -6196,7 +7384,13 @@
         <v>47</v>
       </c>
       <c r="G199" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="H199" s="4" t="n">
         <v>3.9</v>
+      </c>
+      <c r="I199" s="4" t="n">
+        <v>23.4</v>
       </c>
     </row>
     <row r="200">
@@ -6225,7 +7419,13 @@
         <v>22</v>
       </c>
       <c r="G200" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="H200" s="4" t="n">
         <v>3.7</v>
+      </c>
+      <c r="I200" s="4" t="n">
+        <v>22.2</v>
       </c>
     </row>
     <row r="201">
@@ -6254,7 +7454,13 @@
         <v>8</v>
       </c>
       <c r="G201" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H201" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="202">
@@ -6283,7 +7489,13 @@
         <v>3</v>
       </c>
       <c r="G202" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H202" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I202" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="203">
@@ -6312,7 +7524,13 @@
         <v>8</v>
       </c>
       <c r="G203" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H203" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I203" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="204">
@@ -6341,7 +7559,13 @@
         <v>4</v>
       </c>
       <c r="G204" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H204" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I204" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="205">
@@ -6370,7 +7594,13 @@
         <v>3</v>
       </c>
       <c r="G205" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H205" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I205" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="206">
@@ -6399,7 +7629,13 @@
         <v>2</v>
       </c>
       <c r="G206" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H206" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I206" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="207">
@@ -6428,7 +7664,13 @@
         <v>50</v>
       </c>
       <c r="G207" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H207" s="4" t="n">
         <v>4.2</v>
+      </c>
+      <c r="I207" s="4" t="n">
+        <v>25.2</v>
       </c>
     </row>
     <row r="208">
@@ -6457,7 +7699,13 @@
         <v>19</v>
       </c>
       <c r="G208" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="H208" s="4" t="n">
         <v>3.2</v>
+      </c>
+      <c r="I208" s="4" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="209">
@@ -6486,7 +7734,13 @@
         <v>16</v>
       </c>
       <c r="G209" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H209" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I209" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="210">
@@ -6515,7 +7769,13 @@
         <v>30</v>
       </c>
       <c r="G210" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H210" s="4" t="n">
         <v>3.8</v>
+      </c>
+      <c r="I210" s="4" t="n">
+        <v>22.8</v>
       </c>
     </row>
     <row r="211">
@@ -6544,7 +7804,13 @@
         <v>9</v>
       </c>
       <c r="G211" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H211" s="4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I211" s="4" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="212">
@@ -6573,7 +7839,13 @@
         <v>15</v>
       </c>
       <c r="G212" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H212" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="213">
@@ -6602,7 +7874,13 @@
         <v>10</v>
       </c>
       <c r="G213" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H213" s="3" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="214">
@@ -6631,7 +7909,13 @@
         <v>7</v>
       </c>
       <c r="G214" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H214" s="4" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I214" s="4" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="215">
@@ -6660,7 +7944,13 @@
         <v>4</v>
       </c>
       <c r="G215" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H215" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I215" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="216">
@@ -6689,7 +7979,13 @@
         <v>4</v>
       </c>
       <c r="G216" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H216" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="217">
@@ -6718,7 +8014,13 @@
         <v>30</v>
       </c>
       <c r="G217" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H217" s="4" t="n">
         <v>3.3</v>
+      </c>
+      <c r="I217" s="4" t="n">
+        <v>19.8</v>
       </c>
     </row>
     <row r="218">
@@ -6747,7 +8049,13 @@
         <v>12</v>
       </c>
       <c r="G218" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H218" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I218" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="219">
@@ -6776,7 +8084,13 @@
         <v>27</v>
       </c>
       <c r="G219" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="H219" s="3" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I219" s="3" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="220">
@@ -6805,7 +8119,13 @@
         <v>11</v>
       </c>
       <c r="G220" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="H220" s="3" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I220" s="3" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="221">
@@ -6834,7 +8154,13 @@
         <v>41</v>
       </c>
       <c r="G221" s="4" t="n">
+        <v>246</v>
+      </c>
+      <c r="H221" s="4" t="n">
         <v>3.4</v>
+      </c>
+      <c r="I221" s="4" t="n">
+        <v>20.4</v>
       </c>
     </row>
     <row r="222">
@@ -6863,7 +8189,13 @@
         <v>17</v>
       </c>
       <c r="G222" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="H222" s="4" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I222" s="4" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="223">
@@ -6892,7 +8224,13 @@
         <v>23</v>
       </c>
       <c r="G223" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="H223" s="3" t="n">
         <v>1.9</v>
+      </c>
+      <c r="I223" s="3" t="n">
+        <v>11.4</v>
       </c>
     </row>
     <row r="224">
@@ -6921,7 +8259,13 @@
         <v>8</v>
       </c>
       <c r="G224" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H224" s="3" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I224" s="3" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="225">
@@ -6950,7 +8294,13 @@
         <v>14</v>
       </c>
       <c r="G225" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H225" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I225" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="226">
@@ -6979,7 +8329,13 @@
         <v>8</v>
       </c>
       <c r="G226" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H226" s="4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I226" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="227">
@@ -7008,7 +8364,13 @@
         <v>58</v>
       </c>
       <c r="G227" s="3" t="n">
+        <v>348</v>
+      </c>
+      <c r="H227" s="3" t="n">
         <v>29</v>
+      </c>
+      <c r="I227" s="3" t="n">
+        <v>174</v>
       </c>
     </row>
     <row r="228">
@@ -7037,7 +8399,13 @@
         <v>8</v>
       </c>
       <c r="G228" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H228" s="4" t="n">
         <v>4</v>
+      </c>
+      <c r="I228" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="229">
@@ -7066,7 +8434,13 @@
         <v>45</v>
       </c>
       <c r="G229" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="H229" s="3" t="n">
         <v>5.6</v>
+      </c>
+      <c r="I229" s="3" t="n">
+        <v>33.6</v>
       </c>
     </row>
     <row r="230">
@@ -7095,7 +8469,13 @@
         <v>25</v>
       </c>
       <c r="G230" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H230" s="3" t="n">
         <v>5</v>
+      </c>
+      <c r="I230" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="231">
@@ -7124,7 +8504,13 @@
         <v>54</v>
       </c>
       <c r="G231" s="4" t="n">
+        <v>324</v>
+      </c>
+      <c r="H231" s="4" t="n">
         <v>4.9</v>
+      </c>
+      <c r="I231" s="4" t="n">
+        <v>29.4</v>
       </c>
     </row>
     <row r="232">
@@ -7153,7 +8539,13 @@
         <v>23</v>
       </c>
       <c r="G232" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="H232" s="4" t="n">
         <v>3.8</v>
+      </c>
+      <c r="I232" s="4" t="n">
+        <v>22.8</v>
       </c>
     </row>
     <row r="233">
@@ -7182,7 +8574,13 @@
         <v>28</v>
       </c>
       <c r="G233" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="H233" s="3" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I233" s="3" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="234">
@@ -7211,7 +8609,13 @@
         <v>17</v>
       </c>
       <c r="G234" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H234" s="3" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I234" s="3" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="235">
@@ -7240,7 +8644,13 @@
         <v>43</v>
       </c>
       <c r="G235" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="H235" s="4" t="n">
         <v>3.6</v>
+      </c>
+      <c r="I235" s="4" t="n">
+        <v>21.6</v>
       </c>
     </row>
     <row r="236">
@@ -7269,7 +8679,13 @@
         <v>20</v>
       </c>
       <c r="G236" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H236" s="4" t="n">
         <v>3.3</v>
+      </c>
+      <c r="I236" s="4" t="n">
+        <v>19.8</v>
       </c>
     </row>
     <row r="237">
@@ -7298,7 +8714,13 @@
         <v>20</v>
       </c>
       <c r="G237" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H237" s="3" t="n">
         <v>5</v>
+      </c>
+      <c r="I237" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="238">
@@ -7327,7 +8749,13 @@
         <v>10</v>
       </c>
       <c r="G238" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H238" s="3" t="n">
         <v>5</v>
+      </c>
+      <c r="I238" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="239">
@@ -7356,7 +8784,13 @@
         <v>37</v>
       </c>
       <c r="G239" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="H239" s="4" t="n">
         <v>3.1</v>
+      </c>
+      <c r="I239" s="4" t="n">
+        <v>18.6</v>
       </c>
     </row>
     <row r="240">
@@ -7385,7 +8819,13 @@
         <v>17</v>
       </c>
       <c r="G240" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="H240" s="4" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I240" s="4" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="241">
@@ -7414,7 +8854,13 @@
         <v>27</v>
       </c>
       <c r="G241" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="H241" s="3" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I241" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="242">
@@ -7443,7 +8889,13 @@
         <v>12</v>
       </c>
       <c r="G242" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H242" s="3" t="n">
         <v>2.4</v>
+      </c>
+      <c r="I242" s="3" t="n">
+        <v>14.4</v>
       </c>
     </row>
     <row r="243">
@@ -7472,7 +8924,13 @@
         <v>43</v>
       </c>
       <c r="G243" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="H243" s="4" t="n">
         <v>4.8</v>
+      </c>
+      <c r="I243" s="4" t="n">
+        <v>28.8</v>
       </c>
     </row>
     <row r="244">
@@ -7501,7 +8959,13 @@
         <v>20</v>
       </c>
       <c r="G244" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H244" s="4" t="n">
         <v>3.3</v>
+      </c>
+      <c r="I244" s="4" t="n">
+        <v>19.8</v>
       </c>
     </row>
     <row r="245">
@@ -7530,7 +8994,13 @@
         <v>44</v>
       </c>
       <c r="G245" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="H245" s="3" t="n">
         <v>6.3</v>
+      </c>
+      <c r="I245" s="3" t="n">
+        <v>37.8</v>
       </c>
     </row>
     <row r="246">
@@ -7559,7 +9029,13 @@
         <v>25</v>
       </c>
       <c r="G246" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H246" s="3" t="n">
         <v>4.2</v>
+      </c>
+      <c r="I246" s="3" t="n">
+        <v>25.2</v>
       </c>
     </row>
     <row r="247">
@@ -7588,7 +9064,13 @@
         <v>100</v>
       </c>
       <c r="G247" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="H247" s="4" t="n">
         <v>25</v>
+      </c>
+      <c r="I247" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="248">
@@ -7617,7 +9099,13 @@
         <v>25</v>
       </c>
       <c r="G248" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H248" s="4" t="n">
         <v>25</v>
+      </c>
+      <c r="I248" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="249">
@@ -7646,7 +9134,13 @@
         <v>2</v>
       </c>
       <c r="G249" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H249" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I249" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="250">
@@ -7675,7 +9169,13 @@
         <v>5</v>
       </c>
       <c r="G250" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H250" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I250" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="251">
@@ -7704,7 +9204,13 @@
         <v>14</v>
       </c>
       <c r="G251" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H251" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I251" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="252">
@@ -7733,7 +9239,13 @@
         <v>2</v>
       </c>
       <c r="G252" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H252" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I252" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="253">
@@ -7762,7 +9274,13 @@
         <v>3</v>
       </c>
       <c r="G253" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H253" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I253" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="254">
@@ -7791,7 +9309,13 @@
         <v>1</v>
       </c>
       <c r="G254" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H254" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I254" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="255">
@@ -7820,7 +9344,13 @@
         <v>73</v>
       </c>
       <c r="G255" s="3" t="n">
+        <v>438</v>
+      </c>
+      <c r="H255" s="3" t="n">
         <v>7.3</v>
+      </c>
+      <c r="I255" s="3" t="n">
+        <v>43.8</v>
       </c>
     </row>
     <row r="256">
@@ -7849,7 +9379,13 @@
         <v>34</v>
       </c>
       <c r="G256" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="H256" s="3" t="n">
         <v>5.7</v>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="257">
@@ -7878,7 +9414,13 @@
         <v>16</v>
       </c>
       <c r="G257" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H257" s="4" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I257" s="4" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="258">
@@ -7907,7 +9449,13 @@
         <v>4</v>
       </c>
       <c r="G258" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H258" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I258" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="259">
@@ -7936,7 +9484,13 @@
         <v>30</v>
       </c>
       <c r="G259" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="H259" s="3" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I259" s="3" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="260">
@@ -7965,7 +9519,13 @@
         <v>15</v>
       </c>
       <c r="G260" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H260" s="3" t="n">
         <v>3</v>
+      </c>
+      <c r="I260" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="261">
@@ -7994,7 +9554,13 @@
         <v>14</v>
       </c>
       <c r="G261" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H261" s="4" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I261" s="4" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="262">
@@ -8023,7 +9589,13 @@
         <v>6</v>
       </c>
       <c r="G262" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H262" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I262" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="263">
@@ -8052,7 +9624,13 @@
         <v>4</v>
       </c>
       <c r="G263" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H263" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I263" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="264">
@@ -8081,7 +9659,13 @@
         <v>2</v>
       </c>
       <c r="G264" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H264" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I264" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="265">
@@ -8110,7 +9694,13 @@
         <v>2</v>
       </c>
       <c r="G265" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H265" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I265" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="266">
@@ -8139,7 +9729,13 @@
         <v>5</v>
       </c>
       <c r="G266" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H266" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I266" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="267">
@@ -8168,7 +9764,13 @@
         <v>4</v>
       </c>
       <c r="G267" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H267" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I267" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="268">
@@ -8197,7 +9799,13 @@
         <v>11</v>
       </c>
       <c r="G268" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="H268" s="4" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I268" s="4" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="269">
@@ -8226,7 +9834,13 @@
         <v>8</v>
       </c>
       <c r="G269" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H269" s="4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I269" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="270">
@@ -8255,7 +9869,13 @@
         <v>12</v>
       </c>
       <c r="G270" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H270" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I270" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="271">
@@ -8284,7 +9904,13 @@
         <v>7</v>
       </c>
       <c r="G271" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H271" s="3" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I271" s="3" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="272">
@@ -8313,7 +9939,13 @@
         <v>5</v>
       </c>
       <c r="G272" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H272" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I272" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="273">
@@ -8342,7 +9974,13 @@
         <v>4</v>
       </c>
       <c r="G273" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H273" s="3" t="n">
         <v>4</v>
+      </c>
+      <c r="I273" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="274">
@@ -8358,7 +9996,11 @@
       <c r="F274" s="7" t="n">
         <v>2028</v>
       </c>
-      <c r="G274" s="6" t="n"/>
+      <c r="G274" s="7" t="n">
+        <v>12168</v>
+      </c>
+      <c r="H274" s="6" t="n"/>
+      <c r="I274" s="6" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -8386,7 +10028,13 @@
         <v>16</v>
       </c>
       <c r="G275" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H275" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I275" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="276">
@@ -8415,7 +10063,13 @@
         <v>6</v>
       </c>
       <c r="G276" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H276" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I276" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="277">
@@ -8444,7 +10098,13 @@
         <v>32</v>
       </c>
       <c r="G277" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="H277" s="4" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I277" s="4" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="278">
@@ -8473,7 +10133,13 @@
         <v>14</v>
       </c>
       <c r="G278" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H278" s="4" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I278" s="4" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="279">
@@ -8502,7 +10168,13 @@
         <v>22</v>
       </c>
       <c r="G279" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="H279" s="3" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I279" s="3" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="280">
@@ -8531,7 +10203,13 @@
         <v>10</v>
       </c>
       <c r="G280" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H280" s="3" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I280" s="3" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="281">
@@ -8560,7 +10238,13 @@
         <v>53</v>
       </c>
       <c r="G281" s="4" t="n">
+        <v>318</v>
+      </c>
+      <c r="H281" s="4" t="n">
         <v>4.4</v>
+      </c>
+      <c r="I281" s="4" t="n">
+        <v>26.4</v>
       </c>
     </row>
     <row r="282">
@@ -8589,7 +10273,13 @@
         <v>24</v>
       </c>
       <c r="G282" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="H282" s="4" t="n">
         <v>4</v>
+      </c>
+      <c r="I282" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="283">
@@ -8618,7 +10308,13 @@
         <v>74</v>
       </c>
       <c r="G283" s="3" t="n">
+        <v>444</v>
+      </c>
+      <c r="H283" s="3" t="n">
         <v>6.2</v>
+      </c>
+      <c r="I283" s="3" t="n">
+        <v>37.2</v>
       </c>
     </row>
     <row r="284">
@@ -8647,7 +10343,13 @@
         <v>31</v>
       </c>
       <c r="G284" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="H284" s="3" t="n">
         <v>5.2</v>
+      </c>
+      <c r="I284" s="3" t="n">
+        <v>31.2</v>
       </c>
     </row>
     <row r="285">
@@ -8676,7 +10378,13 @@
         <v>58</v>
       </c>
       <c r="G285" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="H285" s="4" t="n">
         <v>4.8</v>
+      </c>
+      <c r="I285" s="4" t="n">
+        <v>28.8</v>
       </c>
     </row>
     <row r="286">
@@ -8705,7 +10413,13 @@
         <v>18</v>
       </c>
       <c r="G286" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="H286" s="4" t="n">
         <v>4.5</v>
+      </c>
+      <c r="I286" s="4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="287">
@@ -8734,7 +10448,13 @@
         <v>8</v>
       </c>
       <c r="G287" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H287" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I287" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="288">
@@ -8763,7 +10483,13 @@
         <v>8</v>
       </c>
       <c r="G288" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H288" s="4" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I288" s="4" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="289">
@@ -8792,7 +10518,13 @@
         <v>12</v>
       </c>
       <c r="G289" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H289" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I289" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="290">
@@ -8821,7 +10553,13 @@
         <v>17</v>
       </c>
       <c r="G290" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H290" s="3" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I290" s="3" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="291">
@@ -8850,7 +10588,13 @@
         <v>7</v>
       </c>
       <c r="G291" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H291" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I291" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="292">
@@ -8879,7 +10623,13 @@
         <v>40</v>
       </c>
       <c r="G292" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="H292" s="4" t="n">
         <v>3.3</v>
+      </c>
+      <c r="I292" s="4" t="n">
+        <v>19.8</v>
       </c>
     </row>
     <row r="293">
@@ -8908,7 +10658,13 @@
         <v>16</v>
       </c>
       <c r="G293" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H293" s="4" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I293" s="4" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="294">
@@ -8937,7 +10693,13 @@
         <v>80</v>
       </c>
       <c r="G294" s="3" t="n">
+        <v>480</v>
+      </c>
+      <c r="H294" s="3" t="n">
         <v>6.7</v>
+      </c>
+      <c r="I294" s="3" t="n">
+        <v>40.2</v>
       </c>
     </row>
     <row r="295">
@@ -8966,7 +10728,13 @@
         <v>10</v>
       </c>
       <c r="G295" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H295" s="3" t="n">
         <v>5</v>
+      </c>
+      <c r="I295" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="296">
@@ -8995,7 +10763,13 @@
         <v>21</v>
       </c>
       <c r="G296" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="H296" s="3" t="n">
         <v>4.2</v>
+      </c>
+      <c r="I296" s="3" t="n">
+        <v>25.2</v>
       </c>
     </row>
     <row r="297">
@@ -9024,7 +10798,13 @@
         <v>85</v>
       </c>
       <c r="G297" s="4" t="n">
+        <v>510</v>
+      </c>
+      <c r="H297" s="4" t="n">
         <v>7.1</v>
+      </c>
+      <c r="I297" s="4" t="n">
+        <v>42.6</v>
       </c>
     </row>
     <row r="298">
@@ -9053,7 +10833,13 @@
         <v>38</v>
       </c>
       <c r="G298" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="H298" s="4" t="n">
         <v>6.3</v>
+      </c>
+      <c r="I298" s="4" t="n">
+        <v>37.8</v>
       </c>
     </row>
     <row r="299">
@@ -9082,7 +10868,13 @@
         <v>11</v>
       </c>
       <c r="G299" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="H299" s="3" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I299" s="3" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="300">
@@ -9111,7 +10903,13 @@
         <v>28</v>
       </c>
       <c r="G300" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="H300" s="4" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I300" s="4" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="301">
@@ -9140,7 +10938,13 @@
         <v>13</v>
       </c>
       <c r="G301" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="H301" s="4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I301" s="4" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="302">
@@ -9169,7 +10973,13 @@
         <v>25</v>
       </c>
       <c r="G302" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H302" s="3" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I302" s="3" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="303">
@@ -9198,7 +11008,13 @@
         <v>5</v>
       </c>
       <c r="G303" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H303" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I303" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="304">
@@ -9227,7 +11043,13 @@
         <v>60</v>
       </c>
       <c r="G304" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="H304" s="4" t="n">
         <v>5</v>
+      </c>
+      <c r="I304" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="305">
@@ -9256,7 +11078,13 @@
         <v>22</v>
       </c>
       <c r="G305" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="H305" s="4" t="n">
         <v>3.7</v>
+      </c>
+      <c r="I305" s="4" t="n">
+        <v>22.2</v>
       </c>
     </row>
     <row r="306">
@@ -9285,7 +11113,13 @@
         <v>40</v>
       </c>
       <c r="G306" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="H306" s="3" t="n">
         <v>3.3</v>
+      </c>
+      <c r="I306" s="3" t="n">
+        <v>19.8</v>
       </c>
     </row>
     <row r="307">
@@ -9314,7 +11148,13 @@
         <v>17</v>
       </c>
       <c r="G307" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H307" s="3" t="n">
         <v>3.4</v>
+      </c>
+      <c r="I307" s="3" t="n">
+        <v>20.4</v>
       </c>
     </row>
     <row r="308">
@@ -9343,7 +11183,13 @@
         <v>51</v>
       </c>
       <c r="G308" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="H308" s="4" t="n">
         <v>4.2</v>
+      </c>
+      <c r="I308" s="4" t="n">
+        <v>25.2</v>
       </c>
     </row>
     <row r="309">
@@ -9372,7 +11218,13 @@
         <v>23</v>
       </c>
       <c r="G309" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="H309" s="4" t="n">
         <v>3.8</v>
+      </c>
+      <c r="I309" s="4" t="n">
+        <v>22.8</v>
       </c>
     </row>
     <row r="310">
@@ -9401,7 +11253,13 @@
         <v>19</v>
       </c>
       <c r="G310" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="H310" s="3" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I310" s="3" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="311">
@@ -9430,7 +11288,13 @@
         <v>7</v>
       </c>
       <c r="G311" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H311" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I311" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="312">
@@ -9459,7 +11323,13 @@
         <v>52</v>
       </c>
       <c r="G312" s="4" t="n">
+        <v>312</v>
+      </c>
+      <c r="H312" s="4" t="n">
         <v>5.2</v>
+      </c>
+      <c r="I312" s="4" t="n">
+        <v>31.2</v>
       </c>
     </row>
     <row r="313">
@@ -9488,7 +11358,13 @@
         <v>38</v>
       </c>
       <c r="G313" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="H313" s="4" t="n">
         <v>6.3</v>
+      </c>
+      <c r="I313" s="4" t="n">
+        <v>37.8</v>
       </c>
     </row>
     <row r="314">
@@ -9517,7 +11393,13 @@
         <v>83</v>
       </c>
       <c r="G314" s="3" t="n">
+        <v>498</v>
+      </c>
+      <c r="H314" s="3" t="n">
         <v>6.9</v>
+      </c>
+      <c r="I314" s="3" t="n">
+        <v>41.4</v>
       </c>
     </row>
     <row r="315">
@@ -9546,7 +11428,13 @@
         <v>46</v>
       </c>
       <c r="G315" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="H315" s="3" t="n">
         <v>7.7</v>
+      </c>
+      <c r="I315" s="3" t="n">
+        <v>46.2</v>
       </c>
     </row>
     <row r="316">
@@ -9575,7 +11463,13 @@
         <v>528</v>
       </c>
       <c r="G316" s="4" t="n">
+        <v>3168</v>
+      </c>
+      <c r="H316" s="4" t="n">
         <v>52.8</v>
+      </c>
+      <c r="I316" s="4" t="n">
+        <v>316.8</v>
       </c>
     </row>
     <row r="317">
@@ -9604,7 +11498,13 @@
         <v>147</v>
       </c>
       <c r="G317" s="4" t="n">
+        <v>882</v>
+      </c>
+      <c r="H317" s="4" t="n">
         <v>36.8</v>
+      </c>
+      <c r="I317" s="4" t="n">
+        <v>220.8</v>
       </c>
     </row>
     <row r="318">
@@ -9633,7 +11533,13 @@
         <v>6</v>
       </c>
       <c r="G318" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H318" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I318" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="319">
@@ -9662,7 +11568,13 @@
         <v>58</v>
       </c>
       <c r="G319" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="H319" s="4" t="n">
         <v>4.8</v>
+      </c>
+      <c r="I319" s="4" t="n">
+        <v>28.8</v>
       </c>
     </row>
     <row r="320">
@@ -9691,7 +11603,13 @@
         <v>22</v>
       </c>
       <c r="G320" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="H320" s="4" t="n">
         <v>4.4</v>
+      </c>
+      <c r="I320" s="4" t="n">
+        <v>26.4</v>
       </c>
     </row>
     <row r="321">
@@ -9720,7 +11638,13 @@
         <v>19</v>
       </c>
       <c r="G321" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="H321" s="3" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I321" s="3" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="322">
@@ -9749,7 +11673,13 @@
         <v>6</v>
       </c>
       <c r="G322" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H322" s="3" t="n">
         <v>1.5</v>
+      </c>
+      <c r="I322" s="3" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="323">
@@ -9778,7 +11708,13 @@
         <v>20</v>
       </c>
       <c r="G323" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H323" s="4" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I323" s="4" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="324">
@@ -9807,7 +11743,13 @@
         <v>8</v>
       </c>
       <c r="G324" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H324" s="4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I324" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="325">
@@ -9836,7 +11778,13 @@
         <v>53</v>
       </c>
       <c r="G325" s="3" t="n">
+        <v>318</v>
+      </c>
+      <c r="H325" s="3" t="n">
         <v>4.4</v>
+      </c>
+      <c r="I325" s="3" t="n">
+        <v>26.4</v>
       </c>
     </row>
     <row r="326">
@@ -9865,7 +11813,13 @@
         <v>25</v>
       </c>
       <c r="G326" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H326" s="3" t="n">
         <v>4.2</v>
+      </c>
+      <c r="I326" s="3" t="n">
+        <v>25.2</v>
       </c>
     </row>
     <row r="327">
@@ -9894,7 +11848,13 @@
         <v>15</v>
       </c>
       <c r="G327" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="H327" s="4" t="n">
         <v>1.5</v>
+      </c>
+      <c r="I327" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="328">
@@ -9923,7 +11883,13 @@
         <v>28</v>
       </c>
       <c r="G328" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="H328" s="3" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I328" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="329">
@@ -9952,7 +11918,13 @@
         <v>12</v>
       </c>
       <c r="G329" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H329" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I329" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="330">
@@ -9981,7 +11953,13 @@
         <v>18</v>
       </c>
       <c r="G330" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="H330" s="4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I330" s="4" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="331">
@@ -10010,7 +11988,13 @@
         <v>2</v>
       </c>
       <c r="G331" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H331" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I331" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="332">
@@ -10039,7 +12023,13 @@
         <v>70</v>
       </c>
       <c r="G332" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="H332" s="4" t="n">
         <v>8.800000000000001</v>
+      </c>
+      <c r="I332" s="4" t="n">
+        <v>52.8</v>
       </c>
     </row>
     <row r="333">
@@ -10068,7 +12058,13 @@
         <v>34</v>
       </c>
       <c r="G333" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="H333" s="4" t="n">
         <v>5.7</v>
+      </c>
+      <c r="I333" s="4" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="334">
@@ -10097,7 +12093,13 @@
         <v>4</v>
       </c>
       <c r="G334" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H334" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I334" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="335">
@@ -10126,7 +12128,13 @@
         <v>5</v>
       </c>
       <c r="G335" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H335" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I335" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="336">
@@ -10155,7 +12163,13 @@
         <v>1</v>
       </c>
       <c r="G336" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H336" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I336" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="337">
@@ -10184,7 +12198,13 @@
         <v>4</v>
       </c>
       <c r="G337" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H337" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I337" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="338">
@@ -10200,7 +12220,11 @@
       <c r="F338" s="7" t="n">
         <v>2325</v>
       </c>
-      <c r="G338" s="6" t="n"/>
+      <c r="G338" s="7" t="n">
+        <v>13950</v>
+      </c>
+      <c r="H338" s="6" t="n"/>
+      <c r="I338" s="6" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -10228,7 +12252,13 @@
         <v>4</v>
       </c>
       <c r="G339" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H339" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I339" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="340">
@@ -10257,7 +12287,13 @@
         <v>4</v>
       </c>
       <c r="G340" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H340" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I340" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="341">
@@ -10286,7 +12322,13 @@
         <v>11</v>
       </c>
       <c r="G341" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="H341" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I341" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="342">
@@ -10315,7 +12357,13 @@
         <v>4</v>
       </c>
       <c r="G342" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H342" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I342" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="343">
@@ -10344,7 +12392,13 @@
         <v>10</v>
       </c>
       <c r="G343" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H343" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I343" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="344">
@@ -10373,7 +12427,13 @@
         <v>5</v>
       </c>
       <c r="G344" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H344" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I344" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="345">
@@ -10402,7 +12462,13 @@
         <v>1</v>
       </c>
       <c r="G345" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H345" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I345" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="346">
@@ -10431,7 +12497,13 @@
         <v>7</v>
       </c>
       <c r="G346" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H346" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I346" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="347">
@@ -10460,7 +12532,13 @@
         <v>3</v>
       </c>
       <c r="G347" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H347" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I347" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="348">
@@ -10489,7 +12567,13 @@
         <v>24</v>
       </c>
       <c r="G348" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="H348" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I348" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="349">
@@ -10518,7 +12602,13 @@
         <v>15</v>
       </c>
       <c r="G349" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H349" s="3" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I349" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="350">
@@ -10547,7 +12637,13 @@
         <v>16</v>
       </c>
       <c r="G350" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H350" s="4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I350" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="351">
@@ -10576,7 +12672,13 @@
         <v>7</v>
       </c>
       <c r="G351" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H351" s="4" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I351" s="4" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="352">
@@ -10605,7 +12707,13 @@
         <v>88</v>
       </c>
       <c r="G352" s="3" t="n">
+        <v>528</v>
+      </c>
+      <c r="H352" s="3" t="n">
         <v>7.3</v>
+      </c>
+      <c r="I352" s="3" t="n">
+        <v>43.8</v>
       </c>
     </row>
     <row r="353">
@@ -10634,7 +12742,13 @@
         <v>44</v>
       </c>
       <c r="G353" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="H353" s="3" t="n">
         <v>7.3</v>
+      </c>
+      <c r="I353" s="3" t="n">
+        <v>43.8</v>
       </c>
     </row>
     <row r="354">
@@ -10663,7 +12777,13 @@
         <v>33</v>
       </c>
       <c r="G354" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="H354" s="4" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I354" s="4" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="355">
@@ -10692,7 +12812,13 @@
         <v>14</v>
       </c>
       <c r="G355" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H355" s="4" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I355" s="4" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="356">
@@ -10721,7 +12847,13 @@
         <v>31</v>
       </c>
       <c r="G356" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="H356" s="3" t="n">
         <v>5.2</v>
+      </c>
+      <c r="I356" s="3" t="n">
+        <v>31.2</v>
       </c>
     </row>
     <row r="357">
@@ -10750,7 +12882,13 @@
         <v>25</v>
       </c>
       <c r="G357" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H357" s="3" t="n">
         <v>4.2</v>
+      </c>
+      <c r="I357" s="3" t="n">
+        <v>25.2</v>
       </c>
     </row>
     <row r="358">
@@ -10779,7 +12917,13 @@
         <v>23</v>
       </c>
       <c r="G358" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="H358" s="3" t="n">
         <v>3.8</v>
+      </c>
+      <c r="I358" s="3" t="n">
+        <v>22.8</v>
       </c>
     </row>
     <row r="359">
@@ -10808,7 +12952,13 @@
         <v>34</v>
       </c>
       <c r="G359" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="H359" s="4" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I359" s="4" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="360">
@@ -10837,7 +12987,13 @@
         <v>5</v>
       </c>
       <c r="G360" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H360" s="4" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I360" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="361">
@@ -10866,7 +13022,13 @@
         <v>78</v>
       </c>
       <c r="G361" s="3" t="n">
+        <v>468</v>
+      </c>
+      <c r="H361" s="3" t="n">
         <v>6.5</v>
+      </c>
+      <c r="I361" s="3" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="362">
@@ -10895,7 +13057,13 @@
         <v>31</v>
       </c>
       <c r="G362" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="H362" s="3" t="n">
         <v>5.2</v>
+      </c>
+      <c r="I362" s="3" t="n">
+        <v>31.2</v>
       </c>
     </row>
     <row r="363">
@@ -10924,7 +13092,13 @@
         <v>20</v>
       </c>
       <c r="G363" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H363" s="4" t="n">
         <v>4</v>
+      </c>
+      <c r="I363" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="364">
@@ -10953,7 +13127,13 @@
         <v>5</v>
       </c>
       <c r="G364" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H364" s="4" t="n">
         <v>5</v>
+      </c>
+      <c r="I364" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="365">
@@ -10982,7 +13162,13 @@
         <v>57</v>
       </c>
       <c r="G365" s="3" t="n">
+        <v>342</v>
+      </c>
+      <c r="H365" s="3" t="n">
         <v>4.8</v>
+      </c>
+      <c r="I365" s="3" t="n">
+        <v>28.8</v>
       </c>
     </row>
     <row r="366">
@@ -11011,7 +13197,13 @@
         <v>22</v>
       </c>
       <c r="G366" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="H366" s="3" t="n">
         <v>3.7</v>
+      </c>
+      <c r="I366" s="3" t="n">
+        <v>22.2</v>
       </c>
     </row>
     <row r="367">
@@ -11040,7 +13232,13 @@
         <v>22</v>
       </c>
       <c r="G367" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="H367" s="4" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I367" s="4" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="368">
@@ -11069,7 +13267,13 @@
         <v>10</v>
       </c>
       <c r="G368" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H368" s="4" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I368" s="4" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="369">
@@ -11098,7 +13302,13 @@
         <v>24</v>
       </c>
       <c r="G369" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="H369" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I369" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="370">
@@ -11127,7 +13337,13 @@
         <v>8</v>
       </c>
       <c r="G370" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H370" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I370" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="371">
@@ -11156,7 +13372,13 @@
         <v>16</v>
       </c>
       <c r="G371" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H371" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I371" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="372">
@@ -11185,7 +13407,13 @@
         <v>47</v>
       </c>
       <c r="G372" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="H372" s="3" t="n">
         <v>3.9</v>
+      </c>
+      <c r="I372" s="3" t="n">
+        <v>23.4</v>
       </c>
     </row>
     <row r="373">
@@ -11214,7 +13442,13 @@
         <v>16</v>
       </c>
       <c r="G373" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H373" s="3" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I373" s="3" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="374">
@@ -11243,7 +13477,13 @@
         <v>6</v>
       </c>
       <c r="G374" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="H374" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I374" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="375">
@@ -11272,7 +13512,13 @@
         <v>24</v>
       </c>
       <c r="G375" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="H375" s="3" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I375" s="3" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="376">
@@ -11301,7 +13547,13 @@
         <v>13</v>
       </c>
       <c r="G376" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="H376" s="3" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I376" s="3" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="377">
@@ -11330,7 +13582,13 @@
         <v>25</v>
       </c>
       <c r="G377" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H377" s="4" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I377" s="4" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="378">
@@ -11359,7 +13617,13 @@
         <v>11</v>
       </c>
       <c r="G378" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="H378" s="4" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I378" s="4" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="379">
@@ -11388,7 +13652,13 @@
         <v>32</v>
       </c>
       <c r="G379" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="H379" s="3" t="n">
         <v>2.9</v>
+      </c>
+      <c r="I379" s="3" t="n">
+        <v>17.4</v>
       </c>
     </row>
     <row r="380">
@@ -11417,7 +13687,13 @@
         <v>14</v>
       </c>
       <c r="G380" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H380" s="3" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I380" s="3" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="381">
@@ -11446,7 +13722,13 @@
         <v>1</v>
       </c>
       <c r="G381" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H381" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I381" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="382">
@@ -11475,7 +13757,13 @@
         <v>39</v>
       </c>
       <c r="G382" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="H382" s="3" t="n">
         <v>3.5</v>
+      </c>
+      <c r="I382" s="3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="383">
@@ -11504,7 +13792,13 @@
         <v>18</v>
       </c>
       <c r="G383" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="H383" s="3" t="n">
         <v>3</v>
+      </c>
+      <c r="I383" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="384">
@@ -11533,7 +13827,13 @@
         <v>15</v>
       </c>
       <c r="G384" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="H384" s="4" t="n">
         <v>2.5</v>
+      </c>
+      <c r="I384" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="385">
@@ -11562,7 +13862,13 @@
         <v>55</v>
       </c>
       <c r="G385" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="H385" s="3" t="n">
         <v>6.1</v>
+      </c>
+      <c r="I385" s="3" t="n">
+        <v>36.6</v>
       </c>
     </row>
     <row r="386">
@@ -11591,7 +13897,13 @@
         <v>25</v>
       </c>
       <c r="G386" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H386" s="3" t="n">
         <v>5</v>
+      </c>
+      <c r="I386" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="387">
@@ -11620,7 +13932,13 @@
         <v>103</v>
       </c>
       <c r="G387" s="4" t="n">
+        <v>618</v>
+      </c>
+      <c r="H387" s="4" t="n">
         <v>10.3</v>
+      </c>
+      <c r="I387" s="4" t="n">
+        <v>61.8</v>
       </c>
     </row>
     <row r="388">
@@ -11649,7 +13967,13 @@
         <v>34</v>
       </c>
       <c r="G388" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="H388" s="4" t="n">
         <v>6.8</v>
+      </c>
+      <c r="I388" s="4" t="n">
+        <v>40.8</v>
       </c>
     </row>
     <row r="389">
@@ -11678,7 +14002,13 @@
         <v>4</v>
       </c>
       <c r="G389" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H389" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I389" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="390">
@@ -11707,7 +14037,13 @@
         <v>21</v>
       </c>
       <c r="G390" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="H390" s="4" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I390" s="4" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="391">
@@ -11736,7 +14072,13 @@
         <v>9</v>
       </c>
       <c r="G391" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H391" s="4" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I391" s="4" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="392">
@@ -11765,7 +14107,13 @@
         <v>41</v>
       </c>
       <c r="G392" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="H392" s="3" t="n">
         <v>3.4</v>
+      </c>
+      <c r="I392" s="3" t="n">
+        <v>20.4</v>
       </c>
     </row>
     <row r="393">
@@ -11794,7 +14142,13 @@
         <v>17</v>
       </c>
       <c r="G393" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H393" s="3" t="n">
         <v>3.4</v>
+      </c>
+      <c r="I393" s="3" t="n">
+        <v>20.4</v>
       </c>
     </row>
     <row r="394">
@@ -11823,7 +14177,13 @@
         <v>11</v>
       </c>
       <c r="G394" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="H394" s="4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I394" s="4" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="395">
@@ -11852,7 +14212,13 @@
         <v>64</v>
       </c>
       <c r="G395" s="3" t="n">
+        <v>384</v>
+      </c>
+      <c r="H395" s="3" t="n">
         <v>5.3</v>
+      </c>
+      <c r="I395" s="3" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="396">
@@ -11881,7 +14247,13 @@
         <v>12</v>
       </c>
       <c r="G396" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H396" s="3" t="n">
         <v>4</v>
+      </c>
+      <c r="I396" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="397">
@@ -11910,7 +14282,13 @@
         <v>84</v>
       </c>
       <c r="G397" s="4" t="n">
+        <v>504</v>
+      </c>
+      <c r="H397" s="4" t="n">
         <v>7</v>
+      </c>
+      <c r="I397" s="4" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="398">
@@ -11939,7 +14317,13 @@
         <v>28</v>
       </c>
       <c r="G398" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="H398" s="4" t="n">
         <v>4.7</v>
+      </c>
+      <c r="I398" s="4" t="n">
+        <v>28.2</v>
       </c>
     </row>
     <row r="399">
@@ -11968,7 +14352,13 @@
         <v>1</v>
       </c>
       <c r="G399" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H399" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I399" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="400">
@@ -11997,7 +14387,13 @@
         <v>16</v>
       </c>
       <c r="G400" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H400" s="4" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I400" s="4" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="401">
@@ -12026,7 +14422,13 @@
         <v>1</v>
       </c>
       <c r="G401" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H401" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I401" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="402">
@@ -12055,7 +14457,13 @@
         <v>14</v>
       </c>
       <c r="G402" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H402" s="3" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I402" s="3" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="403">
@@ -12084,7 +14492,13 @@
         <v>7</v>
       </c>
       <c r="G403" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H403" s="3" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I403" s="3" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="404">
@@ -12113,7 +14527,13 @@
         <v>4</v>
       </c>
       <c r="G404" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H404" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I404" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="405">
@@ -12142,7 +14562,13 @@
         <v>5</v>
       </c>
       <c r="G405" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H405" s="3" t="n">
         <v>5</v>
+      </c>
+      <c r="I405" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="406">
@@ -12171,7 +14597,13 @@
         <v>13</v>
       </c>
       <c r="G406" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="H406" s="4" t="n">
         <v>1.9</v>
+      </c>
+      <c r="I406" s="4" t="n">
+        <v>11.4</v>
       </c>
     </row>
     <row r="407">
@@ -12200,7 +14632,13 @@
         <v>10</v>
       </c>
       <c r="G407" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H407" s="4" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I407" s="4" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="408">
@@ -12229,7 +14667,13 @@
         <v>2</v>
       </c>
       <c r="G408" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H408" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I408" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="409">
@@ -12258,7 +14702,13 @@
         <v>3</v>
       </c>
       <c r="G409" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H409" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I409" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="410">
@@ -12287,7 +14737,13 @@
         <v>9</v>
       </c>
       <c r="G410" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H410" s="4" t="n">
         <v>1.5</v>
+      </c>
+      <c r="I410" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="411">
@@ -12316,7 +14772,13 @@
         <v>17</v>
       </c>
       <c r="G411" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H411" s="3" t="n">
         <v>5.7</v>
+      </c>
+      <c r="I411" s="3" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="412">
@@ -12345,7 +14807,13 @@
         <v>2</v>
       </c>
       <c r="G412" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H412" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I412" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="413">
@@ -12374,7 +14842,13 @@
         <v>3</v>
       </c>
       <c r="G413" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H413" s="3" t="n">
         <v>3</v>
+      </c>
+      <c r="I413" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="414">
@@ -12403,7 +14877,13 @@
         <v>3</v>
       </c>
       <c r="G414" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H414" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I414" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="415">
@@ -12432,7 +14912,13 @@
         <v>1</v>
       </c>
       <c r="G415" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H415" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I415" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="416">
@@ -12448,7 +14934,11 @@
       <c r="F416" s="7" t="n">
         <v>1581</v>
       </c>
-      <c r="G416" s="6" t="n"/>
+      <c r="G416" s="7" t="n">
+        <v>9486</v>
+      </c>
+      <c r="H416" s="6" t="n"/>
+      <c r="I416" s="6" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -12476,7 +14966,13 @@
         <v>15</v>
       </c>
       <c r="G417" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H417" s="3" t="n">
         <v>1.5</v>
+      </c>
+      <c r="I417" s="3" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="418">
@@ -12505,7 +15001,13 @@
         <v>5</v>
       </c>
       <c r="G418" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H418" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I418" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="419">
@@ -12534,7 +15036,13 @@
         <v>25</v>
       </c>
       <c r="G419" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H419" s="4" t="n">
         <v>2.1</v>
+      </c>
+      <c r="I419" s="4" t="n">
+        <v>12.6</v>
       </c>
     </row>
     <row r="420">
@@ -12563,7 +15071,13 @@
         <v>8</v>
       </c>
       <c r="G420" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H420" s="4" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I420" s="4" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="421">
@@ -12592,7 +15106,13 @@
         <v>35</v>
       </c>
       <c r="G421" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="H421" s="3" t="n">
         <v>2.9</v>
+      </c>
+      <c r="I421" s="3" t="n">
+        <v>17.4</v>
       </c>
     </row>
     <row r="422">
@@ -12621,7 +15141,13 @@
         <v>20</v>
       </c>
       <c r="G422" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H422" s="3" t="n">
         <v>3.3</v>
+      </c>
+      <c r="I422" s="3" t="n">
+        <v>19.8</v>
       </c>
     </row>
     <row r="423">
@@ -12650,7 +15176,13 @@
         <v>61</v>
       </c>
       <c r="G423" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="H423" s="4" t="n">
         <v>5.1</v>
+      </c>
+      <c r="I423" s="4" t="n">
+        <v>30.6</v>
       </c>
     </row>
     <row r="424">
@@ -12679,7 +15211,13 @@
         <v>33</v>
       </c>
       <c r="G424" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="H424" s="4" t="n">
         <v>5.5</v>
+      </c>
+      <c r="I424" s="4" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="425">
@@ -12708,7 +15246,13 @@
         <v>14</v>
       </c>
       <c r="G425" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H425" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I425" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="426">
@@ -12737,7 +15281,13 @@
         <v>5</v>
       </c>
       <c r="G426" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H426" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I426" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="427">
@@ -12766,7 +15316,13 @@
         <v>12</v>
       </c>
       <c r="G427" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H427" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I427" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="428">
@@ -12795,7 +15351,13 @@
         <v>7</v>
       </c>
       <c r="G428" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H428" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I428" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="429">
@@ -12824,7 +15386,13 @@
         <v>5</v>
       </c>
       <c r="G429" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H429" s="3" t="n">
         <v>1.7</v>
+      </c>
+      <c r="I429" s="3" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="430">
@@ -12853,7 +15421,13 @@
         <v>11</v>
       </c>
       <c r="G430" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="H430" s="3" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I430" s="3" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="431">
@@ -12882,7 +15456,13 @@
         <v>4</v>
       </c>
       <c r="G431" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H431" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I431" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="432">
@@ -12911,7 +15491,13 @@
         <v>7</v>
       </c>
       <c r="G432" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H432" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I432" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="433">
@@ -12940,7 +15526,13 @@
         <v>4</v>
       </c>
       <c r="G433" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H433" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I433" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="434">
@@ -12969,7 +15561,13 @@
         <v>26</v>
       </c>
       <c r="G434" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="H434" s="3" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I434" s="3" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="435">
@@ -12998,7 +15596,13 @@
         <v>2</v>
       </c>
       <c r="G435" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H435" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I435" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="436">
@@ -13027,7 +15631,13 @@
         <v>46</v>
       </c>
       <c r="G436" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="H436" s="4" t="n">
         <v>3.8</v>
+      </c>
+      <c r="I436" s="4" t="n">
+        <v>22.8</v>
       </c>
     </row>
     <row r="437">
@@ -13056,7 +15666,13 @@
         <v>16</v>
       </c>
       <c r="G437" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H437" s="4" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I437" s="4" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="438">
@@ -13085,7 +15701,13 @@
         <v>32</v>
       </c>
       <c r="G438" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="H438" s="3" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I438" s="3" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="439">
@@ -13114,7 +15736,13 @@
         <v>14</v>
       </c>
       <c r="G439" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H439" s="3" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I439" s="3" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="440">
@@ -13143,7 +15771,13 @@
         <v>12</v>
       </c>
       <c r="G440" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H440" s="4" t="n">
         <v>1.1</v>
+      </c>
+      <c r="I440" s="4" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="441">
@@ -13172,7 +15806,13 @@
         <v>5</v>
       </c>
       <c r="G441" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H441" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I441" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="442">
@@ -13201,7 +15841,13 @@
         <v>32</v>
       </c>
       <c r="G442" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="H442" s="3" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I442" s="3" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="443">
@@ -13230,7 +15876,13 @@
         <v>12</v>
       </c>
       <c r="G443" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H443" s="3" t="n">
         <v>2.4</v>
+      </c>
+      <c r="I443" s="3" t="n">
+        <v>14.4</v>
       </c>
     </row>
     <row r="444">
@@ -13259,7 +15911,13 @@
         <v>33</v>
       </c>
       <c r="G444" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="H444" s="4" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I444" s="4" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="445">
@@ -13288,7 +15946,13 @@
         <v>26</v>
       </c>
       <c r="G445" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="H445" s="3" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I445" s="3" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="446">
@@ -13317,7 +15981,13 @@
         <v>12</v>
       </c>
       <c r="G446" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H446" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I446" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="447">
@@ -13346,7 +16016,13 @@
         <v>53</v>
       </c>
       <c r="G447" s="4" t="n">
+        <v>318</v>
+      </c>
+      <c r="H447" s="4" t="n">
         <v>4.4</v>
+      </c>
+      <c r="I447" s="4" t="n">
+        <v>26.4</v>
       </c>
     </row>
     <row r="448">
@@ -13375,7 +16051,13 @@
         <v>28</v>
       </c>
       <c r="G448" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="H448" s="4" t="n">
         <v>4.7</v>
+      </c>
+      <c r="I448" s="4" t="n">
+        <v>28.2</v>
       </c>
     </row>
     <row r="449">
@@ -13404,7 +16086,13 @@
         <v>19</v>
       </c>
       <c r="G449" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="H449" s="3" t="n">
         <v>1.9</v>
+      </c>
+      <c r="I449" s="3" t="n">
+        <v>11.4</v>
       </c>
     </row>
     <row r="450">
@@ -13433,7 +16121,13 @@
         <v>8</v>
       </c>
       <c r="G450" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H450" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I450" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="451">
@@ -13462,7 +16156,13 @@
         <v>36</v>
       </c>
       <c r="G451" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="H451" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="I451" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="452">
@@ -13491,7 +16191,13 @@
         <v>16</v>
       </c>
       <c r="G452" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H452" s="4" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I452" s="4" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="453">
@@ -13520,7 +16226,13 @@
         <v>42</v>
       </c>
       <c r="G453" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="H453" s="3" t="n">
         <v>3.5</v>
+      </c>
+      <c r="I453" s="3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="454">
@@ -13549,7 +16261,13 @@
         <v>21</v>
       </c>
       <c r="G454" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="H454" s="3" t="n">
         <v>3.5</v>
+      </c>
+      <c r="I454" s="3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="455">
@@ -13578,7 +16296,13 @@
         <v>19</v>
       </c>
       <c r="G455" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="H455" s="4" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I455" s="4" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="456">
@@ -13607,7 +16331,13 @@
         <v>7</v>
       </c>
       <c r="G456" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H456" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I456" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="457">
@@ -13636,7 +16366,13 @@
         <v>98</v>
       </c>
       <c r="G457" s="3" t="n">
+        <v>588</v>
+      </c>
+      <c r="H457" s="3" t="n">
         <v>8.199999999999999</v>
+      </c>
+      <c r="I457" s="3" t="n">
+        <v>49.2</v>
       </c>
     </row>
     <row r="458">
@@ -13665,7 +16401,13 @@
         <v>52</v>
       </c>
       <c r="G458" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="H458" s="3" t="n">
         <v>8.699999999999999</v>
+      </c>
+      <c r="I458" s="3" t="n">
+        <v>52.2</v>
       </c>
     </row>
     <row r="459">
@@ -13694,7 +16436,13 @@
         <v>49</v>
       </c>
       <c r="G459" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="H459" s="4" t="n">
         <v>4.1</v>
+      </c>
+      <c r="I459" s="4" t="n">
+        <v>24.6</v>
       </c>
     </row>
     <row r="460">
@@ -13723,7 +16471,13 @@
         <v>19</v>
       </c>
       <c r="G460" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="H460" s="4" t="n">
         <v>3.2</v>
+      </c>
+      <c r="I460" s="4" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="461">
@@ -13752,7 +16506,13 @@
         <v>145</v>
       </c>
       <c r="G461" s="3" t="n">
+        <v>870</v>
+      </c>
+      <c r="H461" s="3" t="n">
         <v>12.1</v>
+      </c>
+      <c r="I461" s="3" t="n">
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="462">
@@ -13781,7 +16541,13 @@
         <v>64</v>
       </c>
       <c r="G462" s="3" t="n">
+        <v>384</v>
+      </c>
+      <c r="H462" s="3" t="n">
         <v>10.7</v>
+      </c>
+      <c r="I462" s="3" t="n">
+        <v>64.2</v>
       </c>
     </row>
     <row r="463">
@@ -13810,7 +16576,13 @@
         <v>54</v>
       </c>
       <c r="G463" s="4" t="n">
+        <v>324</v>
+      </c>
+      <c r="H463" s="4" t="n">
         <v>10.8</v>
+      </c>
+      <c r="I463" s="4" t="n">
+        <v>64.8</v>
       </c>
     </row>
     <row r="464">
@@ -13839,7 +16611,13 @@
         <v>28</v>
       </c>
       <c r="G464" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="H464" s="4" t="n">
         <v>5.6</v>
+      </c>
+      <c r="I464" s="4" t="n">
+        <v>33.6</v>
       </c>
     </row>
     <row r="465">
@@ -13868,7 +16646,13 @@
         <v>14</v>
       </c>
       <c r="G465" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H465" s="3" t="n">
         <v>2.3</v>
+      </c>
+      <c r="I465" s="3" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="466">
@@ -13897,7 +16681,13 @@
         <v>8</v>
       </c>
       <c r="G466" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H466" s="4" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I466" s="4" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="467">
@@ -13926,7 +16716,13 @@
         <v>24</v>
       </c>
       <c r="G467" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="H467" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I467" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="468">
@@ -13955,7 +16751,13 @@
         <v>7</v>
       </c>
       <c r="G468" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H468" s="3" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I468" s="3" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="469">
@@ -13984,7 +16786,13 @@
         <v>13</v>
       </c>
       <c r="G469" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="H469" s="4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I469" s="4" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="470">
@@ -14013,7 +16821,13 @@
         <v>7</v>
       </c>
       <c r="G470" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H470" s="3" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I470" s="3" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="471">
@@ -14042,7 +16856,13 @@
         <v>2</v>
       </c>
       <c r="G471" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H471" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="I471" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="472">
@@ -14071,7 +16891,13 @@
         <v>7</v>
       </c>
       <c r="G472" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H472" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I472" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="473">
@@ -14100,7 +16926,13 @@
         <v>9</v>
       </c>
       <c r="G473" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H473" s="3" t="n">
         <v>1.3</v>
+      </c>
+      <c r="I473" s="3" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="474">
@@ -14129,7 +16961,13 @@
         <v>1</v>
       </c>
       <c r="G474" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H474" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I474" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="475">
@@ -14158,7 +16996,13 @@
         <v>47</v>
       </c>
       <c r="G475" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="H475" s="4" t="n">
         <v>5.2</v>
+      </c>
+      <c r="I475" s="4" t="n">
+        <v>31.2</v>
       </c>
     </row>
     <row r="476">
@@ -14187,7 +17031,13 @@
         <v>22</v>
       </c>
       <c r="G476" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="H476" s="4" t="n">
         <v>3.7</v>
+      </c>
+      <c r="I476" s="4" t="n">
+        <v>22.2</v>
       </c>
     </row>
     <row r="477">
@@ -14216,7 +17066,13 @@
         <v>16</v>
       </c>
       <c r="G477" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H477" s="3" t="n">
         <v>2.7</v>
+      </c>
+      <c r="I477" s="3" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="478">
@@ -14245,7 +17101,13 @@
         <v>17</v>
       </c>
       <c r="G478" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H478" s="3" t="n">
         <v>2.8</v>
+      </c>
+      <c r="I478" s="3" t="n">
+        <v>16.8</v>
       </c>
     </row>
     <row r="479">
@@ -14274,7 +17136,13 @@
         <v>11</v>
       </c>
       <c r="G479" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="H479" s="4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="I479" s="4" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="480">
@@ -14303,7 +17171,13 @@
         <v>9</v>
       </c>
       <c r="G480" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H480" s="4" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I480" s="4" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="481">
@@ -14332,7 +17206,13 @@
         <v>3</v>
       </c>
       <c r="G481" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H481" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I481" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="482">
@@ -14361,7 +17241,13 @@
         <v>2</v>
       </c>
       <c r="G482" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H482" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I482" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="483">
@@ -14390,7 +17276,13 @@
         <v>49</v>
       </c>
       <c r="G483" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="H483" s="4" t="n">
         <v>4.1</v>
+      </c>
+      <c r="I483" s="4" t="n">
+        <v>24.6</v>
       </c>
     </row>
     <row r="484">
@@ -14419,7 +17311,13 @@
         <v>24</v>
       </c>
       <c r="G484" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="H484" s="4" t="n">
         <v>4</v>
+      </c>
+      <c r="I484" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="485">
@@ -14448,7 +17346,13 @@
         <v>6</v>
       </c>
       <c r="G485" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H485" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="I485" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="486">
@@ -14477,7 +17381,13 @@
         <v>12</v>
       </c>
       <c r="G486" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H486" s="3" t="n">
         <v>2.4</v>
+      </c>
+      <c r="I486" s="3" t="n">
+        <v>14.4</v>
       </c>
     </row>
     <row r="487">
@@ -14506,7 +17416,13 @@
         <v>6</v>
       </c>
       <c r="G487" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="H487" s="4" t="n">
         <v>1.5</v>
+      </c>
+      <c r="I487" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="488">
@@ -14522,7 +17438,11 @@
       <c r="F488" s="7" t="n">
         <v>1613</v>
       </c>
-      <c r="G488" s="6" t="n"/>
+      <c r="G488" s="7" t="n">
+        <v>9678</v>
+      </c>
+      <c r="H488" s="6" t="n"/>
+      <c r="I488" s="6" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -14550,7 +17470,13 @@
         <v>160</v>
       </c>
       <c r="G489" s="3" t="n">
+        <v>960</v>
+      </c>
+      <c r="H489" s="3" t="n">
         <v>13.3</v>
+      </c>
+      <c r="I489" s="3" t="n">
+        <v>79.8</v>
       </c>
     </row>
     <row r="490">
@@ -14579,7 +17505,13 @@
         <v>69</v>
       </c>
       <c r="G490" s="3" t="n">
+        <v>414</v>
+      </c>
+      <c r="H490" s="3" t="n">
         <v>13.8</v>
+      </c>
+      <c r="I490" s="3" t="n">
+        <v>82.8</v>
       </c>
     </row>
     <row r="491">
@@ -14608,7 +17540,13 @@
         <v>32</v>
       </c>
       <c r="G491" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="H491" s="4" t="n">
         <v>10.7</v>
+      </c>
+      <c r="I491" s="4" t="n">
+        <v>64.2</v>
       </c>
     </row>
     <row r="492">
@@ -14637,7 +17575,13 @@
         <v>20</v>
       </c>
       <c r="G492" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H492" s="4" t="n">
         <v>10</v>
+      </c>
+      <c r="I492" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="493">
@@ -14653,7 +17597,11 @@
       <c r="F493" s="7" t="n">
         <v>281</v>
       </c>
-      <c r="G493" s="6" t="n"/>
+      <c r="G493" s="7" t="n">
+        <v>1686</v>
+      </c>
+      <c r="H493" s="6" t="n"/>
+      <c r="I493" s="6" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -14681,7 +17629,13 @@
         <v>10</v>
       </c>
       <c r="G494" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H494" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I494" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="495">
@@ -14710,7 +17664,13 @@
         <v>4</v>
       </c>
       <c r="G495" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H495" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I495" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="496">
@@ -14739,7 +17699,13 @@
         <v>5</v>
       </c>
       <c r="G496" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H496" s="4" t="n">
         <v>1.2</v>
+      </c>
+      <c r="I496" s="4" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="497">
@@ -14768,7 +17734,13 @@
         <v>7</v>
       </c>
       <c r="G497" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H497" s="4" t="n">
         <v>1.4</v>
+      </c>
+      <c r="I497" s="4" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="498">
@@ -14797,7 +17769,13 @@
         <v>7</v>
       </c>
       <c r="G498" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H498" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I498" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="499">
@@ -14826,7 +17804,13 @@
         <v>4</v>
       </c>
       <c r="G499" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H499" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="I499" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="500">
@@ -14855,7 +17839,13 @@
         <v>1</v>
       </c>
       <c r="G500" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H500" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="I500" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="501">
@@ -14871,7 +17861,11 @@
       <c r="F501" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="G501" s="6" t="n"/>
+      <c r="G501" s="7" t="n">
+        <v>228</v>
+      </c>
+      <c r="H501" s="6" t="n"/>
+      <c r="I501" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/relatorio_grao_por_vendedor.xlsx
+++ b/relatorio_grao_por_vendedor.xlsx
@@ -527,10 +527,10 @@
         <v>24</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>24</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="3">
@@ -562,10 +562,10 @@
         <v>528</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>44</v>
+        <v>7.3</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>264</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="4">
@@ -597,10 +597,10 @@
         <v>6</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -632,10 +632,10 @@
         <v>6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
@@ -667,10 +667,10 @@
         <v>6</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
@@ -737,10 +737,10 @@
         <v>12</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -807,10 +807,10 @@
         <v>66</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="11">
@@ -842,10 +842,10 @@
         <v>6</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -1157,10 +1157,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -1227,10 +1227,10 @@
         <v>126</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="23">
@@ -1332,10 +1332,10 @@
         <v>48</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="26">
@@ -1367,10 +1367,10 @@
         <v>66</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="27">
@@ -1402,10 +1402,10 @@
         <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="28">
@@ -1437,10 +1437,10 @@
         <v>102</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="29">
@@ -1507,10 +1507,10 @@
         <v>60</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>15</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="31">
@@ -1542,10 +1542,10 @@
         <v>12</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="32">
@@ -1577,10 +1577,10 @@
         <v>180</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -1647,10 +1647,10 @@
         <v>168</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>24</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="35">
@@ -1752,10 +1752,10 @@
         <v>84</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="38">
@@ -1892,10 +1892,10 @@
         <v>306</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>38.4</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="42">
@@ -1927,10 +1927,10 @@
         <v>150</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>30</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="43">
@@ -1962,10 +1962,10 @@
         <v>300</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>30</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="44">
@@ -1997,10 +1997,10 @@
         <v>120</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>24</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="45">
@@ -2172,10 +2172,10 @@
         <v>366</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>40.8</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="50">
@@ -2312,10 +2312,10 @@
         <v>84</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="54">
@@ -2382,10 +2382,10 @@
         <v>1278</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>21.3</v>
+        <v>17.8</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>127.8</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="56">
@@ -2417,10 +2417,10 @@
         <v>510</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>21.2</v>
+        <v>14.2</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>127.2</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="57">
@@ -2452,10 +2452,10 @@
         <v>6</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="58">
@@ -2557,10 +2557,10 @@
         <v>120</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>24</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="61">
@@ -2627,10 +2627,10 @@
         <v>372</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>37.2</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="63">
@@ -2662,10 +2662,10 @@
         <v>54</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="64">
@@ -2697,10 +2697,10 @@
         <v>12</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="65">
@@ -2732,10 +2732,10 @@
         <v>12</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="66">
@@ -2767,10 +2767,10 @@
         <v>24</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="67">
@@ -2802,10 +2802,10 @@
         <v>420</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>35</v>
+        <v>5.8</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>210</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="68">
@@ -2942,10 +2942,10 @@
         <v>24</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="72">
@@ -2977,10 +2977,10 @@
         <v>12</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="73">
@@ -3082,10 +3082,10 @@
         <v>66</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="76">
@@ -3117,10 +3117,10 @@
         <v>30</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="77">
@@ -3152,10 +3152,10 @@
         <v>48</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="78">
@@ -3187,10 +3187,10 @@
         <v>12</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="79">
@@ -3327,10 +3327,10 @@
         <v>54</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -3362,10 +3362,10 @@
         <v>48</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="84">
@@ -3397,10 +3397,10 @@
         <v>24</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="85">
@@ -3432,10 +3432,10 @@
         <v>48</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="86">
@@ -3467,10 +3467,10 @@
         <v>24</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="87">
@@ -3642,10 +3642,10 @@
         <v>42</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="92">
@@ -3677,10 +3677,10 @@
         <v>18</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -3712,10 +3712,10 @@
         <v>54</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="94">
@@ -3747,10 +3747,10 @@
         <v>30</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="95">
@@ -3817,10 +3817,10 @@
         <v>72</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>14.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97">
@@ -3852,10 +3852,10 @@
         <v>72</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
@@ -3992,10 +3992,10 @@
         <v>114</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="102">
@@ -4062,10 +4062,10 @@
         <v>66</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="104">
@@ -4097,10 +4097,10 @@
         <v>18</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -4132,10 +4132,10 @@
         <v>168</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>16.8</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="106">
@@ -4167,10 +4167,10 @@
         <v>72</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>14.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107">
@@ -4202,10 +4202,10 @@
         <v>18</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="108">
@@ -4237,10 +4237,10 @@
         <v>6</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="109">
@@ -4307,10 +4307,10 @@
         <v>234</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>46.8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="111">
@@ -4377,10 +4377,10 @@
         <v>6</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="113">
@@ -4412,10 +4412,10 @@
         <v>30</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>10.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="114">
@@ -4447,10 +4447,10 @@
         <v>252</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>22.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115">
@@ -4587,10 +4587,10 @@
         <v>18</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="119">
@@ -4797,10 +4797,10 @@
         <v>42</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="125">
@@ -4832,10 +4832,10 @@
         <v>54</v>
       </c>
       <c r="H125" s="4" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>27</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="126">
@@ -4867,10 +4867,10 @@
         <v>90</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127">
@@ -4937,10 +4937,10 @@
         <v>12</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>12</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="129">
@@ -4972,10 +4972,10 @@
         <v>18</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="130">
@@ -5007,10 +5007,10 @@
         <v>96</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>13.8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="131">
@@ -5112,10 +5112,10 @@
         <v>198</v>
       </c>
       <c r="H133" s="4" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>18</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="134">
@@ -5217,10 +5217,10 @@
         <v>60</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="137">
@@ -5252,10 +5252,10 @@
         <v>54</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="138">
@@ -5287,10 +5287,10 @@
         <v>24</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="139">
@@ -5322,10 +5322,10 @@
         <v>30</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="140">
@@ -5357,10 +5357,10 @@
         <v>12</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="141">
@@ -5392,10 +5392,10 @@
         <v>6</v>
       </c>
       <c r="H141" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="142">
@@ -5427,10 +5427,10 @@
         <v>48</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="143">
@@ -5462,10 +5462,10 @@
         <v>18</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -5497,10 +5497,10 @@
         <v>54</v>
       </c>
       <c r="H144" s="4" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="145">
@@ -5567,10 +5567,10 @@
         <v>6</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="147">
@@ -5602,10 +5602,10 @@
         <v>42</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="148">
@@ -5637,10 +5637,10 @@
         <v>24</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="149">
@@ -5672,10 +5672,10 @@
         <v>12</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="150">
@@ -5707,10 +5707,10 @@
         <v>30</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>10.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="151">
@@ -5742,10 +5742,10 @@
         <v>6</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="152">
@@ -5777,10 +5777,10 @@
         <v>24</v>
       </c>
       <c r="H152" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="153">
@@ -5812,10 +5812,10 @@
         <v>18</v>
       </c>
       <c r="H153" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
@@ -5847,10 +5847,10 @@
         <v>24</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="155">
@@ -5882,10 +5882,10 @@
         <v>6</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="156">
@@ -5917,10 +5917,10 @@
         <v>48</v>
       </c>
       <c r="H156" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="157">
@@ -5952,10 +5952,10 @@
         <v>18</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -5987,10 +5987,10 @@
         <v>12</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="159">
@@ -6022,10 +6022,10 @@
         <v>24</v>
       </c>
       <c r="H159" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="160">
@@ -6057,10 +6057,10 @@
         <v>12</v>
       </c>
       <c r="H160" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="161">
@@ -6127,10 +6127,10 @@
         <v>66</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>13.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="163">
@@ -6162,10 +6162,10 @@
         <v>24</v>
       </c>
       <c r="H163" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="164">
@@ -6197,10 +6197,10 @@
         <v>12</v>
       </c>
       <c r="H164" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="165">
@@ -6267,10 +6267,10 @@
         <v>24</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="167">
@@ -6302,10 +6302,10 @@
         <v>30</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>10.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="168">
@@ -6337,10 +6337,10 @@
         <v>18</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -6442,10 +6442,10 @@
         <v>54</v>
       </c>
       <c r="H171" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="172">
@@ -6477,10 +6477,10 @@
         <v>18</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -6687,10 +6687,10 @@
         <v>30</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="179">
@@ -6722,10 +6722,10 @@
         <v>156</v>
       </c>
       <c r="H179" s="4" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>15.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="180">
@@ -6757,10 +6757,10 @@
         <v>54</v>
       </c>
       <c r="H180" s="4" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181">
@@ -6932,10 +6932,10 @@
         <v>90</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="186">
@@ -6967,10 +6967,10 @@
         <v>24</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="187">
@@ -7002,10 +7002,10 @@
         <v>60</v>
       </c>
       <c r="H187" s="4" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>19.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="188">
@@ -7037,10 +7037,10 @@
         <v>24</v>
       </c>
       <c r="H188" s="4" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="189">
@@ -7072,10 +7072,10 @@
         <v>60</v>
       </c>
       <c r="H189" s="4" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>15</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="190">
@@ -7107,10 +7107,10 @@
         <v>66</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="191">
@@ -7142,10 +7142,10 @@
         <v>24</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="192">
@@ -7177,10 +7177,10 @@
         <v>6</v>
       </c>
       <c r="H192" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="193">
@@ -7212,10 +7212,10 @@
         <v>30</v>
       </c>
       <c r="H193" s="4" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="194">
@@ -7387,10 +7387,10 @@
         <v>48</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="199">
@@ -7422,10 +7422,10 @@
         <v>18</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
@@ -7457,10 +7457,10 @@
         <v>48</v>
       </c>
       <c r="H200" s="4" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="201">
@@ -7492,10 +7492,10 @@
         <v>24</v>
       </c>
       <c r="H201" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="202">
@@ -7527,10 +7527,10 @@
         <v>18</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="203">
@@ -7562,10 +7562,10 @@
         <v>12</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="204">
@@ -7702,10 +7702,10 @@
         <v>180</v>
       </c>
       <c r="H207" s="4" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>22.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="208">
@@ -7737,10 +7737,10 @@
         <v>54</v>
       </c>
       <c r="H208" s="4" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>13.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209">
@@ -7842,10 +7842,10 @@
         <v>42</v>
       </c>
       <c r="H211" s="4" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="I211" s="4" t="n">
-        <v>10.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="212">
@@ -7877,10 +7877,10 @@
         <v>24</v>
       </c>
       <c r="H212" s="4" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="213">
@@ -7912,10 +7912,10 @@
         <v>24</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="214">
@@ -7947,10 +7947,10 @@
         <v>180</v>
       </c>
       <c r="H214" s="4" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="I214" s="4" t="n">
-        <v>19.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="215">
@@ -8052,10 +8052,10 @@
         <v>66</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>13.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="218">
@@ -8192,10 +8192,10 @@
         <v>48</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="222">
@@ -8297,10 +8297,10 @@
         <v>348</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>29</v>
+        <v>4.8</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>174</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="225">
@@ -8332,10 +8332,10 @@
         <v>48</v>
       </c>
       <c r="H225" s="4" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>24</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="226">
@@ -8367,10 +8367,10 @@
         <v>270</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>33.6</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="227">
@@ -8402,10 +8402,10 @@
         <v>150</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>30</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="228">
@@ -8437,10 +8437,10 @@
         <v>324</v>
       </c>
       <c r="H228" s="4" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>29.4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="229">
@@ -8507,10 +8507,10 @@
         <v>168</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>16.8</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="231">
@@ -8647,10 +8647,10 @@
         <v>120</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>30</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="235">
@@ -8682,10 +8682,10 @@
         <v>60</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>30</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="236">
@@ -8787,10 +8787,10 @@
         <v>162</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>15</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="239">
@@ -8822,10 +8822,10 @@
         <v>72</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>14.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="240">
@@ -8857,10 +8857,10 @@
         <v>258</v>
       </c>
       <c r="H240" s="4" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="I240" s="4" t="n">
-        <v>28.8</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="241">
@@ -8927,10 +8927,10 @@
         <v>264</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>37.8</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="243">
@@ -8997,10 +8997,10 @@
         <v>600</v>
       </c>
       <c r="H244" s="4" t="n">
-        <v>25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I244" s="4" t="n">
-        <v>150</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="245">
@@ -9032,10 +9032,10 @@
         <v>150</v>
       </c>
       <c r="H245" s="4" t="n">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="I245" s="4" t="n">
-        <v>150</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="246">
@@ -9067,10 +9067,10 @@
         <v>12</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="247">
@@ -9102,10 +9102,10 @@
         <v>30</v>
       </c>
       <c r="H247" s="4" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I247" s="4" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="248">
@@ -9137,10 +9137,10 @@
         <v>84</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="249">
@@ -9172,10 +9172,10 @@
         <v>12</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="250">
@@ -9207,10 +9207,10 @@
         <v>18</v>
       </c>
       <c r="H250" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I250" s="4" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="251">
@@ -9242,10 +9242,10 @@
         <v>6</v>
       </c>
       <c r="H251" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="252">
@@ -9277,10 +9277,10 @@
         <v>438</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>43.8</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="253">
@@ -9347,10 +9347,10 @@
         <v>96</v>
       </c>
       <c r="H254" s="4" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="I254" s="4" t="n">
-        <v>13.8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="255">
@@ -9382,10 +9382,10 @@
         <v>24</v>
       </c>
       <c r="H255" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="256">
@@ -9417,10 +9417,10 @@
         <v>180</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="I256" s="3" t="n">
-        <v>16.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="257">
@@ -9452,10 +9452,10 @@
         <v>90</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I257" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="258">
@@ -9487,10 +9487,10 @@
         <v>84</v>
       </c>
       <c r="H258" s="4" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="I258" s="4" t="n">
-        <v>10.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="259">
@@ -9522,10 +9522,10 @@
         <v>36</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I259" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260">
@@ -9557,10 +9557,10 @@
         <v>24</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="261">
@@ -9592,10 +9592,10 @@
         <v>12</v>
       </c>
       <c r="H261" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I261" s="4" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="262">
@@ -9627,10 +9627,10 @@
         <v>12</v>
       </c>
       <c r="H262" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I262" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="263">
@@ -9662,10 +9662,10 @@
         <v>30</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="264">
@@ -9697,10 +9697,10 @@
         <v>24</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="265">
@@ -9732,10 +9732,10 @@
         <v>66</v>
       </c>
       <c r="H265" s="4" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="I265" s="4" t="n">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="266">
@@ -9837,10 +9837,10 @@
         <v>42</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="269">
@@ -9872,10 +9872,10 @@
         <v>30</v>
       </c>
       <c r="H269" s="4" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I269" s="4" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="270">
@@ -9907,10 +9907,10 @@
         <v>24</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>24</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="271">
@@ -10327,10 +10327,10 @@
         <v>108</v>
       </c>
       <c r="H282" s="4" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="I282" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="283">
@@ -10362,10 +10362,10 @@
         <v>48</v>
       </c>
       <c r="H283" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I283" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="284">
@@ -10397,10 +10397,10 @@
         <v>48</v>
       </c>
       <c r="H284" s="4" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="I284" s="4" t="n">
-        <v>16.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="285">
@@ -10642,10 +10642,10 @@
         <v>60</v>
       </c>
       <c r="H291" s="3" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="I291" s="3" t="n">
-        <v>30</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="292">
@@ -10677,10 +10677,10 @@
         <v>126</v>
       </c>
       <c r="H292" s="3" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I292" s="3" t="n">
-        <v>25.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="293">
@@ -10782,10 +10782,10 @@
         <v>66</v>
       </c>
       <c r="H295" s="3" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="I295" s="3" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="296">
@@ -10887,10 +10887,10 @@
         <v>150</v>
       </c>
       <c r="H298" s="3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="I298" s="3" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="299">
@@ -10922,10 +10922,10 @@
         <v>30</v>
       </c>
       <c r="H299" s="3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I299" s="3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="300">
@@ -11062,10 +11062,10 @@
         <v>102</v>
       </c>
       <c r="H303" s="3" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="I303" s="3" t="n">
-        <v>20.4</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="304">
@@ -11237,10 +11237,10 @@
         <v>312</v>
       </c>
       <c r="H308" s="4" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="I308" s="4" t="n">
-        <v>31.2</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="309">
@@ -11377,10 +11377,10 @@
         <v>3168</v>
       </c>
       <c r="H312" s="4" t="n">
-        <v>52.8</v>
+        <v>44</v>
       </c>
       <c r="I312" s="4" t="n">
-        <v>316.8</v>
+        <v>264</v>
       </c>
     </row>
     <row r="313">
@@ -11412,10 +11412,10 @@
         <v>882</v>
       </c>
       <c r="H313" s="4" t="n">
-        <v>36.8</v>
+        <v>24.5</v>
       </c>
       <c r="I313" s="4" t="n">
-        <v>220.8</v>
+        <v>147</v>
       </c>
     </row>
     <row r="314">
@@ -11447,10 +11447,10 @@
         <v>36</v>
       </c>
       <c r="H314" s="3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I314" s="3" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="315">
@@ -11517,10 +11517,10 @@
         <v>132</v>
       </c>
       <c r="H316" s="4" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="I316" s="4" t="n">
-        <v>26.4</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="317">
@@ -11587,10 +11587,10 @@
         <v>36</v>
       </c>
       <c r="H318" s="3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I318" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="319">
@@ -11762,10 +11762,10 @@
         <v>90</v>
       </c>
       <c r="H323" s="4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="I323" s="4" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="324">
@@ -11797,10 +11797,10 @@
         <v>168</v>
       </c>
       <c r="H324" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="I324" s="3" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="325">
@@ -11867,10 +11867,10 @@
         <v>108</v>
       </c>
       <c r="H326" s="4" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="I326" s="4" t="n">
-        <v>13.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="327">
@@ -11902,10 +11902,10 @@
         <v>12</v>
       </c>
       <c r="H327" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I327" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="328">
@@ -11937,10 +11937,10 @@
         <v>420</v>
       </c>
       <c r="H328" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>52.8</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="329">
@@ -12007,10 +12007,10 @@
         <v>24</v>
       </c>
       <c r="H330" s="3" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="I330" s="3" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="331">
@@ -12042,10 +12042,10 @@
         <v>30</v>
       </c>
       <c r="H331" s="3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I331" s="3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="332">
@@ -12077,10 +12077,10 @@
         <v>6</v>
       </c>
       <c r="H332" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I332" s="4" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="333">
@@ -12112,10 +12112,10 @@
         <v>24</v>
       </c>
       <c r="H333" s="3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="I333" s="3" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="334">
@@ -12147,10 +12147,10 @@
         <v>24</v>
       </c>
       <c r="H334" s="3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I334" s="3" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="335">
@@ -12182,10 +12182,10 @@
         <v>24</v>
       </c>
       <c r="H335" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I335" s="4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="336">
@@ -12217,10 +12217,10 @@
         <v>66</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I336" s="3" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="337">
@@ -12252,10 +12252,10 @@
         <v>24</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="I337" s="3" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="338">
@@ -12287,10 +12287,10 @@
         <v>60</v>
       </c>
       <c r="H338" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="339">
@@ -12322,10 +12322,10 @@
         <v>30</v>
       </c>
       <c r="H339" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I339" s="4" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="340">
@@ -12357,10 +12357,10 @@
         <v>6</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I340" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="341">
@@ -12392,10 +12392,10 @@
         <v>42</v>
       </c>
       <c r="H341" s="4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I341" s="4" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="342">
@@ -12427,10 +12427,10 @@
         <v>18</v>
       </c>
       <c r="H342" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I342" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -12567,10 +12567,10 @@
         <v>42</v>
       </c>
       <c r="H346" s="4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I346" s="4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="347">
@@ -12742,10 +12742,10 @@
         <v>186</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="I351" s="3" t="n">
-        <v>31.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="352">
@@ -12777,10 +12777,10 @@
         <v>150</v>
       </c>
       <c r="H352" s="3" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="I352" s="3" t="n">
-        <v>25.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="353">
@@ -12882,10 +12882,10 @@
         <v>30</v>
       </c>
       <c r="H355" s="4" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>15</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="356">
@@ -12987,10 +12987,10 @@
         <v>120</v>
       </c>
       <c r="H358" s="4" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="I358" s="4" t="n">
-        <v>24</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="359">
@@ -13022,10 +13022,10 @@
         <v>30</v>
       </c>
       <c r="H359" s="4" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="I359" s="4" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="360">
@@ -13267,10 +13267,10 @@
         <v>96</v>
       </c>
       <c r="H366" s="4" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="I366" s="4" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="367">
@@ -13372,10 +13372,10 @@
         <v>36</v>
       </c>
       <c r="H369" s="4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="I369" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="370">
@@ -13407,10 +13407,10 @@
         <v>144</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="I370" s="3" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="371">
@@ -13477,10 +13477,10 @@
         <v>150</v>
       </c>
       <c r="H372" s="4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="I372" s="4" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="373">
@@ -13547,10 +13547,10 @@
         <v>192</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="I374" s="3" t="n">
-        <v>17.4</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="375">
@@ -13582,10 +13582,10 @@
         <v>84</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="I375" s="3" t="n">
-        <v>16.8</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="376">
@@ -13617,10 +13617,10 @@
         <v>6</v>
       </c>
       <c r="H376" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I376" s="4" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="377">
@@ -13652,10 +13652,10 @@
         <v>234</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I377" s="3" t="n">
-        <v>21</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="378">
@@ -13722,10 +13722,10 @@
         <v>90</v>
       </c>
       <c r="H379" s="4" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="I379" s="4" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="380">
@@ -13757,10 +13757,10 @@
         <v>330</v>
       </c>
       <c r="H380" s="3" t="n">
-        <v>6.1</v>
+        <v>4.6</v>
       </c>
       <c r="I380" s="3" t="n">
-        <v>36.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="381">
@@ -13792,10 +13792,10 @@
         <v>150</v>
       </c>
       <c r="H381" s="3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I381" s="3" t="n">
-        <v>30</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="382">
@@ -13827,10 +13827,10 @@
         <v>618</v>
       </c>
       <c r="H382" s="4" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
       <c r="I382" s="4" t="n">
-        <v>61.8</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="383">
@@ -13862,10 +13862,10 @@
         <v>204</v>
       </c>
       <c r="H383" s="4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="I383" s="4" t="n">
-        <v>40.8</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="384">
@@ -13897,10 +13897,10 @@
         <v>24</v>
       </c>
       <c r="H384" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I384" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="385">
@@ -13967,10 +13967,10 @@
         <v>54</v>
       </c>
       <c r="H386" s="4" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I386" s="4" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="387">
@@ -14037,10 +14037,10 @@
         <v>102</v>
       </c>
       <c r="H388" s="3" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="I388" s="3" t="n">
-        <v>20.4</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="389">
@@ -14072,10 +14072,10 @@
         <v>66</v>
       </c>
       <c r="H389" s="4" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="I389" s="4" t="n">
-        <v>13.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="390">
@@ -14142,10 +14142,10 @@
         <v>72</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I391" s="3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="392">
@@ -14247,10 +14247,10 @@
         <v>6</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I394" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="395">
@@ -14282,10 +14282,10 @@
         <v>96</v>
       </c>
       <c r="H395" s="4" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I395" s="4" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="396">
@@ -14317,10 +14317,10 @@
         <v>6</v>
       </c>
       <c r="H396" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I396" s="4" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="397">
@@ -14352,10 +14352,10 @@
         <v>84</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="I397" s="3" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="398">
@@ -14387,10 +14387,10 @@
         <v>42</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I398" s="3" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="399">
@@ -14422,10 +14422,10 @@
         <v>24</v>
       </c>
       <c r="H399" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I399" s="4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="400">
@@ -14457,10 +14457,10 @@
         <v>30</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="I400" s="3" t="n">
-        <v>30</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="401">
@@ -14492,10 +14492,10 @@
         <v>78</v>
       </c>
       <c r="H401" s="4" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="I401" s="4" t="n">
-        <v>11.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="402">
@@ -14562,10 +14562,10 @@
         <v>12</v>
       </c>
       <c r="H403" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I403" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="404">
@@ -14597,10 +14597,10 @@
         <v>18</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I404" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
@@ -14667,10 +14667,10 @@
         <v>102</v>
       </c>
       <c r="H406" s="3" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="I406" s="3" t="n">
-        <v>34.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="407">
@@ -14702,10 +14702,10 @@
         <v>12</v>
       </c>
       <c r="H407" s="4" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="I407" s="4" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="408">
@@ -14737,10 +14737,10 @@
         <v>18</v>
       </c>
       <c r="H408" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I408" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="I408" s="3" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="409">
@@ -14772,10 +14772,10 @@
         <v>18</v>
       </c>
       <c r="H409" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I409" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -14807,10 +14807,10 @@
         <v>6</v>
       </c>
       <c r="H410" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I410" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="411">
@@ -14842,10 +14842,10 @@
         <v>90</v>
       </c>
       <c r="H411" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="I411" s="3" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="412">
@@ -14877,10 +14877,10 @@
         <v>30</v>
       </c>
       <c r="H412" s="3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I412" s="3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="413">
@@ -14947,10 +14947,10 @@
         <v>48</v>
       </c>
       <c r="H414" s="4" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I414" s="4" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="415">
@@ -15122,10 +15122,10 @@
         <v>84</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I419" s="3" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="420">
@@ -15157,10 +15157,10 @@
         <v>30</v>
       </c>
       <c r="H420" s="3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I420" s="3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="421">
@@ -15192,10 +15192,10 @@
         <v>72</v>
       </c>
       <c r="H421" s="4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I421" s="4" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="422">
@@ -15262,10 +15262,10 @@
         <v>30</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="I423" s="3" t="n">
-        <v>10.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="424">
@@ -15297,10 +15297,10 @@
         <v>66</v>
       </c>
       <c r="H424" s="3" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="I424" s="3" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="425">
@@ -15332,10 +15332,10 @@
         <v>24</v>
       </c>
       <c r="H425" s="3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="I425" s="3" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="426">
@@ -15367,10 +15367,10 @@
         <v>42</v>
       </c>
       <c r="H426" s="4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I426" s="4" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="427">
@@ -15402,10 +15402,10 @@
         <v>24</v>
       </c>
       <c r="H427" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I427" s="4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="428">
@@ -15472,10 +15472,10 @@
         <v>12</v>
       </c>
       <c r="H429" s="3" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="I429" s="3" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="430">
@@ -15647,10 +15647,10 @@
         <v>72</v>
       </c>
       <c r="H434" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I434" s="4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="435">
@@ -15682,10 +15682,10 @@
         <v>30</v>
       </c>
       <c r="H435" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I435" s="4" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="436">
@@ -15752,10 +15752,10 @@
         <v>72</v>
       </c>
       <c r="H437" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I437" s="3" t="n">
-        <v>14.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="438">
@@ -15962,10 +15962,10 @@
         <v>114</v>
       </c>
       <c r="H443" s="3" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="I443" s="3" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="444">
@@ -16452,10 +16452,10 @@
         <v>324</v>
       </c>
       <c r="H457" s="4" t="n">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
       <c r="I457" s="4" t="n">
-        <v>64.8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="458">
@@ -16487,10 +16487,10 @@
         <v>168</v>
       </c>
       <c r="H458" s="4" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="I458" s="4" t="n">
-        <v>33.6</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="459">
@@ -16557,10 +16557,10 @@
         <v>48</v>
       </c>
       <c r="H460" s="4" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I460" s="4" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="461">
@@ -16627,10 +16627,10 @@
         <v>42</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I462" s="3" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="463">
@@ -16697,10 +16697,10 @@
         <v>42</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="I464" s="3" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="465">
@@ -16732,10 +16732,10 @@
         <v>12</v>
       </c>
       <c r="H465" s="4" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="I465" s="4" t="n">
-        <v>12</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="466">
@@ -16802,10 +16802,10 @@
         <v>54</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="I467" s="3" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="468">
@@ -16837,10 +16837,10 @@
         <v>6</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I468" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="469">
@@ -16872,10 +16872,10 @@
         <v>282</v>
       </c>
       <c r="H469" s="4" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="I469" s="4" t="n">
-        <v>31.2</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="470">
@@ -16942,10 +16942,10 @@
         <v>96</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="I471" s="3" t="n">
-        <v>16.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="472">
@@ -17012,10 +17012,10 @@
         <v>66</v>
       </c>
       <c r="H473" s="4" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="I473" s="4" t="n">
-        <v>13.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="474">
@@ -17047,10 +17047,10 @@
         <v>54</v>
       </c>
       <c r="H474" s="4" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I474" s="4" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="475">
@@ -17082,10 +17082,10 @@
         <v>18</v>
       </c>
       <c r="H475" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I475" s="3" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="476">
@@ -17117,10 +17117,10 @@
         <v>12</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I476" s="3" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="477">
@@ -17222,10 +17222,10 @@
         <v>36</v>
       </c>
       <c r="H479" s="3" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="I479" s="3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -17257,10 +17257,10 @@
         <v>72</v>
       </c>
       <c r="H480" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I480" s="3" t="n">
-        <v>14.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="481">
@@ -17292,10 +17292,10 @@
         <v>36</v>
       </c>
       <c r="H481" s="4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I481" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="482">
@@ -17362,10 +17362,10 @@
         <v>414</v>
       </c>
       <c r="H483" s="3" t="n">
-        <v>13.8</v>
+        <v>11.5</v>
       </c>
       <c r="I483" s="3" t="n">
-        <v>82.8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="484">
@@ -17397,10 +17397,10 @@
         <v>192</v>
       </c>
       <c r="H484" s="4" t="n">
-        <v>10.7</v>
+        <v>2.7</v>
       </c>
       <c r="I484" s="4" t="n">
-        <v>64.2</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="485">
@@ -17432,10 +17432,10 @@
         <v>120</v>
       </c>
       <c r="H485" s="4" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="I485" s="4" t="n">
-        <v>60</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="486">
@@ -17467,10 +17467,10 @@
         <v>60</v>
       </c>
       <c r="H486" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I486" s="3" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="487">
@@ -17502,10 +17502,10 @@
         <v>24</v>
       </c>
       <c r="H487" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I487" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="488">
@@ -17537,10 +17537,10 @@
         <v>30</v>
       </c>
       <c r="H488" s="4" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="I488" s="4" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="489">
@@ -17572,10 +17572,10 @@
         <v>42</v>
       </c>
       <c r="H489" s="4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I489" s="4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="490">
@@ -17607,10 +17607,10 @@
         <v>42</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I490" s="3" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="491">
@@ -17642,10 +17642,10 @@
         <v>24</v>
       </c>
       <c r="H491" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I491" s="3" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="492">
@@ -17677,10 +17677,10 @@
         <v>6</v>
       </c>
       <c r="H492" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I492" s="4" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_grao_por_vendedor.xlsx
+++ b/relatorio_grao_por_vendedor.xlsx
@@ -527,10 +527,10 @@
         <v>24</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>1.8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -562,10 +562,10 @@
         <v>528</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>7.3</v>
+        <v>44</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>43.8</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4">
@@ -597,10 +597,10 @@
         <v>6</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -632,10 +632,10 @@
         <v>6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -667,10 +667,10 @@
         <v>6</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -737,10 +737,10 @@
         <v>12</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -842,10 +842,10 @@
         <v>6</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1157,10 +1157,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="21">
@@ -1402,10 +1402,10 @@
         <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="28">
@@ -1437,10 +1437,10 @@
         <v>102</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.4</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="29">
@@ -1507,10 +1507,10 @@
         <v>60</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -1542,10 +1542,10 @@
         <v>12</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -1577,10 +1577,10 @@
         <v>180</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1647,10 +1647,10 @@
         <v>168</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13.8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -1752,10 +1752,10 @@
         <v>84</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="38">
@@ -1892,10 +1892,10 @@
         <v>306</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>25.2</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="42">
@@ -1927,10 +1927,10 @@
         <v>150</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>25.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
@@ -1997,10 +1997,10 @@
         <v>120</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>19.8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
@@ -2172,10 +2172,10 @@
         <v>366</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>30.6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50">
@@ -2312,10 +2312,10 @@
         <v>84</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="54">
@@ -2382,10 +2382,10 @@
         <v>1278</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>106.8</v>
+        <v>116.4</v>
       </c>
     </row>
     <row r="56">
@@ -2417,10 +2417,10 @@
         <v>510</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>14.2</v>
+        <v>17</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>85.2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57">
@@ -2452,10 +2452,10 @@
         <v>6</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -2557,10 +2557,10 @@
         <v>120</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>10.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -2627,10 +2627,10 @@
         <v>372</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>31.2</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="63">
@@ -2697,10 +2697,10 @@
         <v>12</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2732,10 +2732,10 @@
         <v>12</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -2767,10 +2767,10 @@
         <v>24</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="67">
@@ -2802,10 +2802,10 @@
         <v>420</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>5.8</v>
+        <v>35</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>34.8</v>
+        <v>210</v>
       </c>
     </row>
     <row r="68">
@@ -2942,10 +2942,10 @@
         <v>24</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="72">
@@ -2977,10 +2977,10 @@
         <v>12</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -3082,10 +3082,10 @@
         <v>66</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -3152,10 +3152,10 @@
         <v>48</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="78">
@@ -3187,10 +3187,10 @@
         <v>12</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="79">
@@ -3327,10 +3327,10 @@
         <v>54</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="83">
@@ -3397,10 +3397,10 @@
         <v>24</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="85">
@@ -3432,10 +3432,10 @@
         <v>48</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="86">
@@ -3467,10 +3467,10 @@
         <v>24</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
@@ -3677,10 +3677,10 @@
         <v>18</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="93">
@@ -3817,10 +3817,10 @@
         <v>72</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>12</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="97">
@@ -4097,10 +4097,10 @@
         <v>18</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="105">
@@ -4132,10 +4132,10 @@
         <v>168</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106">
@@ -4167,10 +4167,10 @@
         <v>72</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>12</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="107">
@@ -4202,10 +4202,10 @@
         <v>18</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="108">
@@ -4237,10 +4237,10 @@
         <v>6</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
@@ -4307,10 +4307,10 @@
         <v>234</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>39</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="111">
@@ -4377,10 +4377,10 @@
         <v>6</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
@@ -4412,10 +4412,10 @@
         <v>30</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>2.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="114">
@@ -4447,10 +4447,10 @@
         <v>252</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>21</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="115">
@@ -4587,10 +4587,10 @@
         <v>18</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="119">
@@ -4797,10 +4797,10 @@
         <v>42</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="125">
@@ -4832,10 +4832,10 @@
         <v>54</v>
       </c>
       <c r="H125" s="4" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126">
@@ -4867,10 +4867,10 @@
         <v>90</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127">
@@ -4937,10 +4937,10 @@
         <v>12</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>1.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129">
@@ -4972,10 +4972,10 @@
         <v>18</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>1.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130">
@@ -5007,10 +5007,10 @@
         <v>96</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131">
@@ -5112,10 +5112,10 @@
         <v>198</v>
       </c>
       <c r="H133" s="4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134">
@@ -5217,10 +5217,10 @@
         <v>60</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>10.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137">
@@ -5252,10 +5252,10 @@
         <v>54</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="138">
@@ -5287,10 +5287,10 @@
         <v>24</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="139">
@@ -5322,10 +5322,10 @@
         <v>30</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -5357,10 +5357,10 @@
         <v>12</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="141">
@@ -5392,10 +5392,10 @@
         <v>6</v>
       </c>
       <c r="H141" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142">
@@ -5427,10 +5427,10 @@
         <v>48</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="143">
@@ -5462,10 +5462,10 @@
         <v>18</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="144">
@@ -5497,10 +5497,10 @@
         <v>54</v>
       </c>
       <c r="H144" s="4" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="145">
@@ -5567,10 +5567,10 @@
         <v>6</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
@@ -5602,10 +5602,10 @@
         <v>42</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148">
@@ -5637,10 +5637,10 @@
         <v>24</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149">
@@ -5672,10 +5672,10 @@
         <v>12</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="150">
@@ -5707,10 +5707,10 @@
         <v>30</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>4.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="151">
@@ -5742,10 +5742,10 @@
         <v>6</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152">
@@ -5777,10 +5777,10 @@
         <v>24</v>
       </c>
       <c r="H152" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="153">
@@ -5847,10 +5847,10 @@
         <v>24</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
@@ -5882,10 +5882,10 @@
         <v>6</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156">
@@ -5952,10 +5952,10 @@
         <v>18</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="158">
@@ -5987,10 +5987,10 @@
         <v>12</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="159">
@@ -6022,10 +6022,10 @@
         <v>24</v>
       </c>
       <c r="H159" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="160">
@@ -6057,10 +6057,10 @@
         <v>12</v>
       </c>
       <c r="H160" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -6127,10 +6127,10 @@
         <v>66</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>10.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="163">
@@ -6162,10 +6162,10 @@
         <v>24</v>
       </c>
       <c r="H163" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="164">
@@ -6197,10 +6197,10 @@
         <v>12</v>
       </c>
       <c r="H164" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -6267,10 +6267,10 @@
         <v>24</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="167">
@@ -6302,10 +6302,10 @@
         <v>30</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="168">
@@ -6337,10 +6337,10 @@
         <v>18</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="169">
@@ -6477,10 +6477,10 @@
         <v>18</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="173">
@@ -6687,10 +6687,10 @@
         <v>30</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179">
@@ -6757,10 +6757,10 @@
         <v>54</v>
       </c>
       <c r="H180" s="4" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="181">
@@ -6932,10 +6932,10 @@
         <v>90</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="186">
@@ -6967,10 +6967,10 @@
         <v>24</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="187">
@@ -7002,10 +7002,10 @@
         <v>60</v>
       </c>
       <c r="H187" s="4" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>4.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="188">
@@ -7037,10 +7037,10 @@
         <v>24</v>
       </c>
       <c r="H188" s="4" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189">
@@ -7177,10 +7177,10 @@
         <v>6</v>
       </c>
       <c r="H192" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193">
@@ -7212,10 +7212,10 @@
         <v>30</v>
       </c>
       <c r="H193" s="4" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="194">
@@ -7422,10 +7422,10 @@
         <v>18</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="200">
@@ -7457,10 +7457,10 @@
         <v>48</v>
       </c>
       <c r="H200" s="4" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201">
@@ -7492,10 +7492,10 @@
         <v>24</v>
       </c>
       <c r="H201" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="202">
@@ -7527,10 +7527,10 @@
         <v>18</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="203">
@@ -7562,10 +7562,10 @@
         <v>12</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="204">
@@ -7702,10 +7702,10 @@
         <v>180</v>
       </c>
       <c r="H207" s="4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208">
@@ -7737,10 +7737,10 @@
         <v>54</v>
       </c>
       <c r="H208" s="4" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="209">
@@ -7842,10 +7842,10 @@
         <v>42</v>
       </c>
       <c r="H211" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I211" s="4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="212">
@@ -7877,10 +7877,10 @@
         <v>24</v>
       </c>
       <c r="H212" s="4" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213">
@@ -7912,10 +7912,10 @@
         <v>24</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="214">
@@ -7947,10 +7947,10 @@
         <v>180</v>
       </c>
       <c r="H214" s="4" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="I214" s="4" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="215">
@@ -8052,10 +8052,10 @@
         <v>66</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>10.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="218">
@@ -8192,10 +8192,10 @@
         <v>48</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="222">
@@ -8297,10 +8297,10 @@
         <v>348</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>4.8</v>
+        <v>29</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>28.8</v>
+        <v>174</v>
       </c>
     </row>
     <row r="225">
@@ -8332,10 +8332,10 @@
         <v>48</v>
       </c>
       <c r="H225" s="4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>4.2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="226">
@@ -8367,10 +8367,10 @@
         <v>270</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="227">
@@ -8437,10 +8437,10 @@
         <v>324</v>
       </c>
       <c r="H228" s="4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>27</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="229">
@@ -8507,10 +8507,10 @@
         <v>168</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="231">
@@ -8647,10 +8647,10 @@
         <v>120</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>10.2</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="235">
@@ -8682,10 +8682,10 @@
         <v>60</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>10.2</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="236">
@@ -8822,10 +8822,10 @@
         <v>72</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>12</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="240">
@@ -8857,10 +8857,10 @@
         <v>258</v>
       </c>
       <c r="H240" s="4" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I240" s="4" t="n">
-        <v>21.6</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="241">
@@ -8927,10 +8927,10 @@
         <v>264</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>22.2</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="243">
@@ -8997,10 +8997,10 @@
         <v>600</v>
       </c>
       <c r="H244" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="I244" s="4" t="n">
-        <v>49.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="245">
@@ -9032,10 +9032,10 @@
         <v>150</v>
       </c>
       <c r="H245" s="4" t="n">
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="I245" s="4" t="n">
-        <v>25.2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="246">
@@ -9067,10 +9067,10 @@
         <v>12</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="247">
@@ -9102,10 +9102,10 @@
         <v>30</v>
       </c>
       <c r="H247" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I247" s="4" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="248">
@@ -9172,10 +9172,10 @@
         <v>12</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="250">
@@ -9207,10 +9207,10 @@
         <v>18</v>
       </c>
       <c r="H250" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I250" s="4" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="251">
@@ -9242,10 +9242,10 @@
         <v>6</v>
       </c>
       <c r="H251" s="4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="252">
@@ -9277,10 +9277,10 @@
         <v>438</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>36.6</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="253">
@@ -9382,10 +9382,10 @@
         <v>24</v>
       </c>
       <c r="H255" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="256">
@@ -9487,10 +9487,10 @@
         <v>84</v>
       </c>
       <c r="H258" s="4" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="I258" s="4" t="n">
-        <v>7.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="259">
@@ -9522,10 +9522,10 @@
         <v>36</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I259" s="3" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="260">
@@ -9592,10 +9592,10 @@
         <v>12</v>
       </c>
       <c r="H261" s="4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I261" s="4" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262">
@@ -9627,10 +9627,10 @@
         <v>12</v>
       </c>
       <c r="H262" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I262" s="4" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263">
@@ -9662,10 +9662,10 @@
         <v>30</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="264">
@@ -9697,10 +9697,10 @@
         <v>24</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="265">
@@ -9732,10 +9732,10 @@
         <v>66</v>
       </c>
       <c r="H265" s="4" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="I265" s="4" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="266">
@@ -9837,10 +9837,10 @@
         <v>42</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="269">
@@ -9872,10 +9872,10 @@
         <v>30</v>
       </c>
       <c r="H269" s="4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I269" s="4" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="270">
@@ -9907,10 +9907,10 @@
         <v>24</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>4.2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="271">
@@ -10327,10 +10327,10 @@
         <v>108</v>
       </c>
       <c r="H282" s="4" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="I282" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="283">
@@ -10362,10 +10362,10 @@
         <v>48</v>
       </c>
       <c r="H283" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I283" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="284">
@@ -10397,10 +10397,10 @@
         <v>48</v>
       </c>
       <c r="H284" s="4" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="I284" s="4" t="n">
-        <v>4.2</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="285">
@@ -10642,10 +10642,10 @@
         <v>60</v>
       </c>
       <c r="H291" s="3" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="I291" s="3" t="n">
-        <v>10.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="292">
@@ -10677,10 +10677,10 @@
         <v>126</v>
       </c>
       <c r="H292" s="3" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="I292" s="3" t="n">
-        <v>21</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="293">
@@ -10782,10 +10782,10 @@
         <v>66</v>
       </c>
       <c r="H295" s="3" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I295" s="3" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="296">
@@ -10922,10 +10922,10 @@
         <v>30</v>
       </c>
       <c r="H299" s="3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I299" s="3" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="300">
@@ -11377,10 +11377,10 @@
         <v>3168</v>
       </c>
       <c r="H312" s="4" t="n">
-        <v>44</v>
+        <v>52.8</v>
       </c>
       <c r="I312" s="4" t="n">
-        <v>264</v>
+        <v>316.8</v>
       </c>
     </row>
     <row r="313">
@@ -11412,10 +11412,10 @@
         <v>882</v>
       </c>
       <c r="H313" s="4" t="n">
-        <v>24.5</v>
+        <v>29.4</v>
       </c>
       <c r="I313" s="4" t="n">
-        <v>147</v>
+        <v>176.4</v>
       </c>
     </row>
     <row r="314">
@@ -11517,10 +11517,10 @@
         <v>132</v>
       </c>
       <c r="H316" s="4" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="I316" s="4" t="n">
-        <v>22.2</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="317">
@@ -11587,10 +11587,10 @@
         <v>36</v>
       </c>
       <c r="H318" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I318" s="3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="319">
@@ -11867,10 +11867,10 @@
         <v>108</v>
       </c>
       <c r="H326" s="4" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="I326" s="4" t="n">
-        <v>9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="327">
@@ -11902,10 +11902,10 @@
         <v>12</v>
       </c>
       <c r="H327" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I327" s="3" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="328">
@@ -11937,10 +11937,10 @@
         <v>420</v>
       </c>
       <c r="H328" s="4" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>34.8</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="329">
@@ -12007,10 +12007,10 @@
         <v>24</v>
       </c>
       <c r="H330" s="3" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="I330" s="3" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="331">
@@ -12077,10 +12077,10 @@
         <v>6</v>
       </c>
       <c r="H332" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I332" s="4" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="333">
@@ -12112,10 +12112,10 @@
         <v>24</v>
       </c>
       <c r="H333" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="I333" s="3" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="334">
@@ -12147,10 +12147,10 @@
         <v>24</v>
       </c>
       <c r="H334" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I334" s="3" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -12182,10 +12182,10 @@
         <v>24</v>
       </c>
       <c r="H335" s="4" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I335" s="4" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="336">
@@ -12217,10 +12217,10 @@
         <v>66</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I336" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="337">
@@ -12252,10 +12252,10 @@
         <v>24</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="I337" s="3" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="338">
@@ -12287,10 +12287,10 @@
         <v>60</v>
       </c>
       <c r="H338" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="339">
@@ -12357,10 +12357,10 @@
         <v>6</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I340" s="3" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="341">
@@ -12427,10 +12427,10 @@
         <v>18</v>
       </c>
       <c r="H342" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I342" s="4" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="343">
@@ -12742,10 +12742,10 @@
         <v>186</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="I351" s="3" t="n">
-        <v>15.6</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="352">
@@ -12777,10 +12777,10 @@
         <v>150</v>
       </c>
       <c r="H352" s="3" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="I352" s="3" t="n">
-        <v>12.6</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="353">
@@ -12882,10 +12882,10 @@
         <v>30</v>
       </c>
       <c r="H355" s="4" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="356">
@@ -12987,10 +12987,10 @@
         <v>120</v>
       </c>
       <c r="H358" s="4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I358" s="4" t="n">
-        <v>10.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="359">
@@ -13022,10 +13022,10 @@
         <v>30</v>
       </c>
       <c r="H359" s="4" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="I359" s="4" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="360">
@@ -13267,10 +13267,10 @@
         <v>96</v>
       </c>
       <c r="H366" s="4" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="I366" s="4" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="367">
@@ -13372,10 +13372,10 @@
         <v>36</v>
       </c>
       <c r="H369" s="4" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="I369" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="370">
@@ -13582,10 +13582,10 @@
         <v>84</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="I375" s="3" t="n">
-        <v>13.8</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="376">
@@ -13617,10 +13617,10 @@
         <v>6</v>
       </c>
       <c r="H376" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I376" s="4" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="377">
@@ -13722,10 +13722,10 @@
         <v>90</v>
       </c>
       <c r="H379" s="4" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="I379" s="4" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="380">
@@ -13757,10 +13757,10 @@
         <v>330</v>
       </c>
       <c r="H380" s="3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I380" s="3" t="n">
-        <v>27.6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="381">
@@ -13792,10 +13792,10 @@
         <v>150</v>
       </c>
       <c r="H381" s="3" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I381" s="3" t="n">
-        <v>25.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="382">
@@ -13862,10 +13862,10 @@
         <v>204</v>
       </c>
       <c r="H383" s="4" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="I383" s="4" t="n">
-        <v>34.2</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="384">
@@ -13897,10 +13897,10 @@
         <v>24</v>
       </c>
       <c r="H384" s="3" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I384" s="3" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="385">
@@ -14037,10 +14037,10 @@
         <v>102</v>
       </c>
       <c r="H388" s="3" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="I388" s="3" t="n">
-        <v>16.8</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="389">
@@ -14072,10 +14072,10 @@
         <v>66</v>
       </c>
       <c r="H389" s="4" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="I389" s="4" t="n">
-        <v>5.4</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="390">
@@ -14142,10 +14142,10 @@
         <v>72</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I391" s="3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="392">
@@ -14247,10 +14247,10 @@
         <v>6</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I394" s="3" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="395">
@@ -14282,10 +14282,10 @@
         <v>96</v>
       </c>
       <c r="H395" s="4" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="I395" s="4" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="396">
@@ -14317,10 +14317,10 @@
         <v>6</v>
       </c>
       <c r="H396" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I396" s="4" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="397">
@@ -14352,10 +14352,10 @@
         <v>84</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="I397" s="3" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="398">
@@ -14387,10 +14387,10 @@
         <v>42</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I398" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="399">
@@ -14422,10 +14422,10 @@
         <v>24</v>
       </c>
       <c r="H399" s="4" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I399" s="4" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="400">
@@ -14457,10 +14457,10 @@
         <v>30</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="I400" s="3" t="n">
-        <v>2.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="401">
@@ -14492,10 +14492,10 @@
         <v>78</v>
       </c>
       <c r="H401" s="4" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="I401" s="4" t="n">
-        <v>6.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="402">
@@ -14562,10 +14562,10 @@
         <v>12</v>
       </c>
       <c r="H403" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I403" s="3" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="404">
@@ -14597,10 +14597,10 @@
         <v>18</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I404" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="405">
@@ -14667,10 +14667,10 @@
         <v>102</v>
       </c>
       <c r="H406" s="3" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="I406" s="3" t="n">
-        <v>16.8</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="407">
@@ -14702,10 +14702,10 @@
         <v>12</v>
       </c>
       <c r="H407" s="4" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="I407" s="4" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="408">
@@ -14737,10 +14737,10 @@
         <v>18</v>
       </c>
       <c r="H408" s="3" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="I408" s="3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="409">
@@ -14772,10 +14772,10 @@
         <v>18</v>
       </c>
       <c r="H409" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I409" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="410">
@@ -14807,10 +14807,10 @@
         <v>6</v>
       </c>
       <c r="H410" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I410" s="3" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="411">
@@ -14842,10 +14842,10 @@
         <v>90</v>
       </c>
       <c r="H411" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I411" s="3" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="412">
@@ -14877,10 +14877,10 @@
         <v>30</v>
       </c>
       <c r="H412" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I412" s="3" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="413">
@@ -14947,10 +14947,10 @@
         <v>48</v>
       </c>
       <c r="H414" s="4" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="I414" s="4" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="415">
@@ -15157,10 +15157,10 @@
         <v>30</v>
       </c>
       <c r="H420" s="3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I420" s="3" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="421">
@@ -15262,10 +15262,10 @@
         <v>30</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="I423" s="3" t="n">
-        <v>4.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="424">
@@ -15297,10 +15297,10 @@
         <v>66</v>
       </c>
       <c r="H424" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I424" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="425">
@@ -15332,10 +15332,10 @@
         <v>24</v>
       </c>
       <c r="H425" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="I425" s="3" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="426">
@@ -15472,10 +15472,10 @@
         <v>12</v>
       </c>
       <c r="H429" s="3" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="I429" s="3" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="430">
@@ -15682,10 +15682,10 @@
         <v>30</v>
       </c>
       <c r="H435" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I435" s="4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="436">
@@ -15752,10 +15752,10 @@
         <v>72</v>
       </c>
       <c r="H437" s="3" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I437" s="3" t="n">
-        <v>12</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="438">
@@ -15962,10 +15962,10 @@
         <v>114</v>
       </c>
       <c r="H443" s="3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I443" s="3" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="444">
@@ -16452,10 +16452,10 @@
         <v>324</v>
       </c>
       <c r="H457" s="4" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="I457" s="4" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="458">
@@ -16487,10 +16487,10 @@
         <v>168</v>
       </c>
       <c r="H458" s="4" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="I458" s="4" t="n">
-        <v>28.2</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="459">
@@ -16557,10 +16557,10 @@
         <v>48</v>
       </c>
       <c r="H460" s="4" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="I460" s="4" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="461">
@@ -16732,10 +16732,10 @@
         <v>12</v>
       </c>
       <c r="H465" s="4" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="I465" s="4" t="n">
-        <v>1.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="466">
@@ -16802,10 +16802,10 @@
         <v>54</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I467" s="3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="468">
@@ -16837,10 +16837,10 @@
         <v>6</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I468" s="3" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="469">
@@ -16872,10 +16872,10 @@
         <v>282</v>
       </c>
       <c r="H469" s="4" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="I469" s="4" t="n">
-        <v>23.4</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="470">
@@ -16942,10 +16942,10 @@
         <v>96</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="I471" s="3" t="n">
-        <v>7.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="472">
@@ -17012,10 +17012,10 @@
         <v>66</v>
       </c>
       <c r="H473" s="4" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="I473" s="4" t="n">
-        <v>5.4</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="474">
@@ -17047,10 +17047,10 @@
         <v>54</v>
       </c>
       <c r="H474" s="4" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="I474" s="4" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="475">
@@ -17082,10 +17082,10 @@
         <v>18</v>
       </c>
       <c r="H475" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I475" s="3" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="476">
@@ -17117,10 +17117,10 @@
         <v>12</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I476" s="3" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="477">
@@ -17222,10 +17222,10 @@
         <v>36</v>
       </c>
       <c r="H479" s="3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="I479" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="480">
@@ -17292,10 +17292,10 @@
         <v>36</v>
       </c>
       <c r="H481" s="4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I481" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="482">
@@ -17362,10 +17362,10 @@
         <v>414</v>
       </c>
       <c r="H483" s="3" t="n">
-        <v>11.5</v>
+        <v>13.8</v>
       </c>
       <c r="I483" s="3" t="n">
-        <v>69</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="484">
@@ -17397,10 +17397,10 @@
         <v>192</v>
       </c>
       <c r="H484" s="4" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="I484" s="4" t="n">
-        <v>16.2</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="485">
@@ -17432,10 +17432,10 @@
         <v>120</v>
       </c>
       <c r="H485" s="4" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="I485" s="4" t="n">
-        <v>19.8</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="486">
@@ -17467,10 +17467,10 @@
         <v>60</v>
       </c>
       <c r="H486" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I486" s="3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="487">
@@ -17502,10 +17502,10 @@
         <v>24</v>
       </c>
       <c r="H487" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I487" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="488">
@@ -17537,10 +17537,10 @@
         <v>30</v>
       </c>
       <c r="H488" s="4" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="I488" s="4" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="489">
@@ -17572,10 +17572,10 @@
         <v>42</v>
       </c>
       <c r="H489" s="4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I489" s="4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="490">
@@ -17677,10 +17677,10 @@
         <v>6</v>
       </c>
       <c r="H492" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I492" s="4" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_grao_por_vendedor.xlsx
+++ b/relatorio_grao_por_vendedor.xlsx
@@ -527,10 +527,10 @@
         <v>24</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>4</v>
+        <v>121.8</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>24</v>
+        <v>730.8</v>
       </c>
     </row>
     <row r="3">
@@ -562,10 +562,10 @@
         <v>528</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>44</v>
+        <v>95.7</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>264</v>
+        <v>574.2</v>
       </c>
     </row>
     <row r="4">
@@ -597,10 +597,10 @@
         <v>6</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="5">
@@ -632,10 +632,10 @@
         <v>6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="6">
@@ -667,10 +667,10 @@
         <v>6</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="7">
@@ -702,10 +702,10 @@
         <v>276</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>22.8</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="8">
@@ -737,10 +737,10 @@
         <v>138</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -772,10 +772,10 @@
         <v>66</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -807,10 +807,10 @@
         <v>6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="11">
@@ -842,10 +842,10 @@
         <v>150</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="12">
@@ -877,10 +877,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -912,10 +912,10 @@
         <v>96</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -947,10 +947,10 @@
         <v>42</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -982,10 +982,10 @@
         <v>282</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="16">
@@ -1017,10 +1017,10 @@
         <v>132</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>22.2</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="17">
@@ -1052,10 +1052,10 @@
         <v>84</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="18">
@@ -1087,10 +1087,10 @@
         <v>42</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="19">
@@ -1122,10 +1122,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="20">
@@ -1157,10 +1157,10 @@
         <v>36</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="21">
@@ -1192,10 +1192,10 @@
         <v>126</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="22">
@@ -1227,10 +1227,10 @@
         <v>60</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>10.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="23">
@@ -1262,10 +1262,10 @@
         <v>108</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="24">
@@ -1297,10 +1297,10 @@
         <v>48</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="25">
@@ -1332,10 +1332,10 @@
         <v>66</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1367,10 +1367,10 @@
         <v>24</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="27">
@@ -1402,10 +1402,10 @@
         <v>102</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>14.4</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="28">
@@ -1437,10 +1437,10 @@
         <v>186</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>15.6</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="29">
@@ -1472,10 +1472,10 @@
         <v>72</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="30">
@@ -1507,10 +1507,10 @@
         <v>180</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>30</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="31">
@@ -1542,10 +1542,10 @@
         <v>126</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>21</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="32">
@@ -1577,10 +1577,10 @@
         <v>168</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>24</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="33">
@@ -1612,10 +1612,10 @@
         <v>408</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>34.2</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="34">
@@ -1647,10 +1647,10 @@
         <v>192</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>31.8</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="35">
@@ -1682,10 +1682,10 @@
         <v>84</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -1717,10 +1717,10 @@
         <v>42</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="37">
@@ -1752,10 +1752,10 @@
         <v>192</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
@@ -1787,10 +1787,10 @@
         <v>84</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>13.8</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="39">
@@ -1822,10 +1822,10 @@
         <v>306</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>34.2</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="40">
@@ -1857,10 +1857,10 @@
         <v>150</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>30</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="41">
@@ -1892,10 +1892,10 @@
         <v>300</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>25.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="42">
@@ -1927,10 +1927,10 @@
         <v>120</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>24</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="43">
@@ -1962,10 +1962,10 @@
         <v>240</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
@@ -1997,10 +1997,10 @@
         <v>84</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>13.8</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="45">
@@ -2032,10 +2032,10 @@
         <v>720</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46">
@@ -2067,10 +2067,10 @@
         <v>342</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>57</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2102,10 +2102,10 @@
         <v>366</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>33</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="48">
@@ -2137,10 +2137,10 @@
         <v>138</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
@@ -2172,10 +2172,10 @@
         <v>282</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>23.4</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="50">
@@ -2207,10 +2207,10 @@
         <v>144</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -2242,10 +2242,10 @@
         <v>84</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="52">
@@ -2277,10 +2277,10 @@
         <v>48</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="53">
@@ -2312,10 +2312,10 @@
         <v>1278</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>116.4</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="54">
@@ -2347,10 +2347,10 @@
         <v>510</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>17</v>
+        <v>22.7</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>102</v>
+        <v>136.2</v>
       </c>
     </row>
     <row r="55">
@@ -2382,10 +2382,10 @@
         <v>6</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="56">
@@ -2417,10 +2417,10 @@
         <v>330</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>27.6</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="57">
@@ -2452,10 +2452,10 @@
         <v>174</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>28.8</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="58">
@@ -2487,10 +2487,10 @@
         <v>120</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>15</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="59">
@@ -2522,10 +2522,10 @@
         <v>90</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
@@ -2557,10 +2557,10 @@
         <v>372</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>33.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
@@ -2592,10 +2592,10 @@
         <v>54</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="62">
@@ -2627,10 +2627,10 @@
         <v>12</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="63">
@@ -2662,10 +2662,10 @@
         <v>12</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="64">
@@ -2697,10 +2697,10 @@
         <v>24</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="65">
@@ -2732,10 +2732,10 @@
         <v>420</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>35</v>
+        <v>62.7</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>210</v>
+        <v>376.2</v>
       </c>
     </row>
     <row r="66">
@@ -2767,10 +2767,10 @@
         <v>198</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>33</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="67">
@@ -2802,10 +2802,10 @@
         <v>180</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="68">
@@ -2837,10 +2837,10 @@
         <v>84</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>13.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="69">
@@ -2907,10 +2907,10 @@
         <v>12</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="71">
@@ -2942,10 +2942,10 @@
         <v>180</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="72">
@@ -2977,10 +2977,10 @@
         <v>90</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73">
@@ -3012,10 +3012,10 @@
         <v>66</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="74">
@@ -3047,10 +3047,10 @@
         <v>30</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="75">
@@ -3117,10 +3117,10 @@
         <v>12</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -3152,10 +3152,10 @@
         <v>150</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>12.6</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="78">
@@ -3187,10 +3187,10 @@
         <v>78</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>13.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
@@ -3222,10 +3222,10 @@
         <v>138</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
@@ -3257,10 +3257,10 @@
         <v>54</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>10.8</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="81">
@@ -3292,10 +3292,10 @@
         <v>48</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="82">
@@ -3327,10 +3327,10 @@
         <v>24</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="83">
@@ -3362,10 +3362,10 @@
         <v>48</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="84">
@@ -3397,10 +3397,10 @@
         <v>24</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="85">
@@ -3432,10 +3432,10 @@
         <v>162</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="86">
@@ -3467,10 +3467,10 @@
         <v>66</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="87">
@@ -3502,10 +3502,10 @@
         <v>132</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="88">
@@ -3537,10 +3537,10 @@
         <v>60</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="89">
@@ -3572,10 +3572,10 @@
         <v>42</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="90">
@@ -3607,10 +3607,10 @@
         <v>18</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="91">
@@ -3642,10 +3642,10 @@
         <v>54</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="92">
@@ -3677,10 +3677,10 @@
         <v>30</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -3712,10 +3712,10 @@
         <v>174</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="94">
@@ -3747,10 +3747,10 @@
         <v>72</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="95">
@@ -3782,10 +3782,10 @@
         <v>72</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="96">
@@ -3817,10 +3817,10 @@
         <v>36</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="97">
@@ -3852,10 +3852,10 @@
         <v>252</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>21</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="98">
@@ -3887,10 +3887,10 @@
         <v>108</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>18</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="99">
@@ -3922,10 +3922,10 @@
         <v>114</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="100">
@@ -3957,10 +3957,10 @@
         <v>36</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="101">
@@ -3992,10 +3992,10 @@
         <v>66</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
@@ -4027,10 +4027,10 @@
         <v>18</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="103">
@@ -4062,10 +4062,10 @@
         <v>168</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="104">
@@ -4097,10 +4097,10 @@
         <v>72</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>14.4</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="105">
@@ -4167,10 +4167,10 @@
         <v>6</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="107">
@@ -4202,10 +4202,10 @@
         <v>264</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="108">
@@ -4237,10 +4237,10 @@
         <v>234</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>46.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="109">
@@ -4272,10 +4272,10 @@
         <v>408</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>34.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="110">
@@ -4307,10 +4307,10 @@
         <v>6</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="111">
@@ -4342,10 +4342,10 @@
         <v>30</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>10.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="112">
@@ -4377,10 +4377,10 @@
         <v>252</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>22.8</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="113">
@@ -4412,10 +4412,10 @@
         <v>132</v>
       </c>
       <c r="H113" s="4" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>22.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="114">
@@ -4447,10 +4447,10 @@
         <v>384</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="115">
@@ -4482,10 +4482,10 @@
         <v>186</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>31.2</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="116">
@@ -4517,10 +4517,10 @@
         <v>18</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="117">
@@ -4552,10 +4552,10 @@
         <v>138</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>11.4</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="118">
@@ -4587,10 +4587,10 @@
         <v>66</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>10.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="119">
@@ -4622,10 +4622,10 @@
         <v>546</v>
       </c>
       <c r="H119" s="4" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>45.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="120">
@@ -4657,10 +4657,10 @@
         <v>258</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>43.2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="121">
@@ -4692,10 +4692,10 @@
         <v>90</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="122">
@@ -4727,10 +4727,10 @@
         <v>42</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>8.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="123">
@@ -4762,10 +4762,10 @@
         <v>54</v>
       </c>
       <c r="H123" s="4" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>18</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="124">
@@ -4797,10 +4797,10 @@
         <v>90</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125">
@@ -4832,10 +4832,10 @@
         <v>150</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>25.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="126">
@@ -4867,10 +4867,10 @@
         <v>12</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>12</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="127">
@@ -4902,10 +4902,10 @@
         <v>18</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
     </row>
     <row r="128">
@@ -4937,10 +4937,10 @@
         <v>96</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="129">
@@ -4972,10 +4972,10 @@
         <v>456</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>37.8</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="130">
@@ -5007,10 +5007,10 @@
         <v>180</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>30</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="131">
@@ -5042,10 +5042,10 @@
         <v>198</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="132">
@@ -5077,10 +5077,10 @@
         <v>108</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>18</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="133">
@@ -5112,10 +5112,10 @@
         <v>132</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>10.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="134">
@@ -5147,10 +5147,10 @@
         <v>60</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135">
@@ -5182,10 +5182,10 @@
         <v>54</v>
       </c>
       <c r="H135" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136">
@@ -5217,10 +5217,10 @@
         <v>24</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="137">
@@ -5252,10 +5252,10 @@
         <v>30</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="138">
@@ -5287,10 +5287,10 @@
         <v>12</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
@@ -5322,10 +5322,10 @@
         <v>6</v>
       </c>
       <c r="H139" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="140">
@@ -5392,10 +5392,10 @@
         <v>18</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="142">
@@ -5427,10 +5427,10 @@
         <v>54</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="143">
@@ -5462,10 +5462,10 @@
         <v>48</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="144">
@@ -5497,10 +5497,10 @@
         <v>6</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="145">
@@ -5532,10 +5532,10 @@
         <v>42</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="146">
@@ -5567,10 +5567,10 @@
         <v>24</v>
       </c>
       <c r="H146" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="147">
@@ -5602,10 +5602,10 @@
         <v>12</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="148">
@@ -5637,10 +5637,10 @@
         <v>30</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>10.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149">
@@ -5672,10 +5672,10 @@
         <v>6</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="150">
@@ -5707,10 +5707,10 @@
         <v>24</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -5742,10 +5742,10 @@
         <v>18</v>
       </c>
       <c r="H151" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="152">
@@ -5812,10 +5812,10 @@
         <v>6</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="154">
@@ -5882,10 +5882,10 @@
         <v>18</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="156">
@@ -5917,10 +5917,10 @@
         <v>12</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -5987,10 +5987,10 @@
         <v>12</v>
       </c>
       <c r="H158" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="159">
@@ -6022,10 +6022,10 @@
         <v>132</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160">
@@ -6057,10 +6057,10 @@
         <v>66</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="161">
@@ -6092,10 +6092,10 @@
         <v>24</v>
       </c>
       <c r="H161" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -6127,10 +6127,10 @@
         <v>12</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="163">
@@ -6162,10 +6162,10 @@
         <v>78</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="164">
@@ -6197,10 +6197,10 @@
         <v>24</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165">
@@ -6232,10 +6232,10 @@
         <v>30</v>
       </c>
       <c r="H165" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="166">
@@ -6267,10 +6267,10 @@
         <v>18</v>
       </c>
       <c r="H166" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167">
@@ -6302,10 +6302,10 @@
         <v>216</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="168">
@@ -6337,10 +6337,10 @@
         <v>78</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="169">
@@ -6372,10 +6372,10 @@
         <v>54</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="170">
@@ -6407,10 +6407,10 @@
         <v>18</v>
       </c>
       <c r="H170" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="171">
@@ -6442,10 +6442,10 @@
         <v>468</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>39</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="172">
@@ -6477,10 +6477,10 @@
         <v>186</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>31.2</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="173">
@@ -6512,10 +6512,10 @@
         <v>168</v>
       </c>
       <c r="H173" s="4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="174">
@@ -6547,10 +6547,10 @@
         <v>78</v>
       </c>
       <c r="H174" s="4" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="175">
@@ -6582,10 +6582,10 @@
         <v>102</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="176">
@@ -6617,10 +6617,10 @@
         <v>30</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="177">
@@ -6652,10 +6652,10 @@
         <v>156</v>
       </c>
       <c r="H177" s="4" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="178">
@@ -6687,10 +6687,10 @@
         <v>54</v>
       </c>
       <c r="H178" s="4" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>13.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179">
@@ -6722,10 +6722,10 @@
         <v>234</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>19.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="180">
@@ -6757,10 +6757,10 @@
         <v>108</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>18</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="181">
@@ -6792,10 +6792,10 @@
         <v>228</v>
       </c>
       <c r="H181" s="4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>19.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="182">
@@ -6827,10 +6827,10 @@
         <v>84</v>
       </c>
       <c r="H182" s="4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>13.8</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="183">
@@ -6862,10 +6862,10 @@
         <v>90</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184">
@@ -6897,10 +6897,10 @@
         <v>24</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185">
@@ -6932,10 +6932,10 @@
         <v>84</v>
       </c>
       <c r="H185" s="4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186">
@@ -6967,10 +6967,10 @@
         <v>60</v>
       </c>
       <c r="H186" s="4" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>10.2</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="187">
@@ -7002,10 +7002,10 @@
         <v>66</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188">
@@ -7037,10 +7037,10 @@
         <v>24</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="189">
@@ -7072,10 +7072,10 @@
         <v>6</v>
       </c>
       <c r="H189" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="190">
@@ -7107,10 +7107,10 @@
         <v>30</v>
       </c>
       <c r="H190" s="4" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>7.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="191">
@@ -7142,10 +7142,10 @@
         <v>234</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>19.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="192">
@@ -7177,10 +7177,10 @@
         <v>96</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="193">
@@ -7212,10 +7212,10 @@
         <v>282</v>
       </c>
       <c r="H193" s="4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>23.4</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="194">
@@ -7247,10 +7247,10 @@
         <v>132</v>
       </c>
       <c r="H194" s="4" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>22.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="195">
@@ -7352,10 +7352,10 @@
         <v>48</v>
       </c>
       <c r="H197" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I197" s="4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="198">
@@ -7387,10 +7387,10 @@
         <v>24</v>
       </c>
       <c r="H198" s="4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="199">
@@ -7422,10 +7422,10 @@
         <v>18</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
@@ -7457,10 +7457,10 @@
         <v>12</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="201">
@@ -7492,10 +7492,10 @@
         <v>300</v>
       </c>
       <c r="H201" s="4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>25.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="202">
@@ -7527,10 +7527,10 @@
         <v>114</v>
       </c>
       <c r="H202" s="4" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>19.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="203">
@@ -7562,10 +7562,10 @@
         <v>96</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="204">
@@ -7597,10 +7597,10 @@
         <v>180</v>
       </c>
       <c r="H204" s="4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>18</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="205">
@@ -7632,10 +7632,10 @@
         <v>54</v>
       </c>
       <c r="H205" s="4" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="206">
@@ -7667,10 +7667,10 @@
         <v>90</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="207">
@@ -7702,10 +7702,10 @@
         <v>60</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>10.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208">
@@ -7737,10 +7737,10 @@
         <v>42</v>
       </c>
       <c r="H208" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="209">
@@ -7772,10 +7772,10 @@
         <v>24</v>
       </c>
       <c r="H209" s="4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="210">
@@ -7842,10 +7842,10 @@
         <v>180</v>
       </c>
       <c r="H211" s="4" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="I211" s="4" t="n">
-        <v>16.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="212">
@@ -7877,10 +7877,10 @@
         <v>72</v>
       </c>
       <c r="H212" s="4" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>12</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="213">
@@ -7912,10 +7912,10 @@
         <v>162</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="214">
@@ -7947,10 +7947,10 @@
         <v>66</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="215">
@@ -7982,10 +7982,10 @@
         <v>246</v>
       </c>
       <c r="H215" s="4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I215" s="4" t="n">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="216">
@@ -8017,10 +8017,10 @@
         <v>102</v>
       </c>
       <c r="H216" s="4" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="I216" s="4" t="n">
-        <v>16.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="217">
@@ -8052,10 +8052,10 @@
         <v>138</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>11.4</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="218">
@@ -8087,10 +8087,10 @@
         <v>48</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="219">
@@ -8122,10 +8122,10 @@
         <v>84</v>
       </c>
       <c r="H219" s="4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I219" s="4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="220">
@@ -8157,10 +8157,10 @@
         <v>48</v>
       </c>
       <c r="H220" s="4" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I220" s="4" t="n">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="221">
@@ -8192,10 +8192,10 @@
         <v>348</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>174</v>
+        <v>204</v>
       </c>
     </row>
     <row r="222">
@@ -8227,10 +8227,10 @@
         <v>48</v>
       </c>
       <c r="H222" s="4" t="n">
-        <v>4</v>
+        <v>14.3</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>24</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="223">
@@ -8262,10 +8262,10 @@
         <v>270</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>27</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="224">
@@ -8297,10 +8297,10 @@
         <v>150</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>25.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="225">
@@ -8332,10 +8332,10 @@
         <v>324</v>
       </c>
       <c r="H225" s="4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>29.4</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="226">
@@ -8367,10 +8367,10 @@
         <v>138</v>
       </c>
       <c r="H226" s="4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I226" s="4" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="227">
@@ -8402,10 +8402,10 @@
         <v>168</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="228">
@@ -8437,10 +8437,10 @@
         <v>102</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>16.8</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="229">
@@ -8472,10 +8472,10 @@
         <v>258</v>
       </c>
       <c r="H229" s="4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="230">
@@ -8507,10 +8507,10 @@
         <v>120</v>
       </c>
       <c r="H230" s="4" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="I230" s="4" t="n">
-        <v>19.8</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="231">
@@ -8542,10 +8542,10 @@
         <v>120</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I231" s="3" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="232">
@@ -8577,10 +8577,10 @@
         <v>60</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>19.8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="233">
@@ -8612,10 +8612,10 @@
         <v>222</v>
       </c>
       <c r="H233" s="4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I233" s="4" t="n">
-        <v>18.6</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="234">
@@ -8647,10 +8647,10 @@
         <v>102</v>
       </c>
       <c r="H234" s="4" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="I234" s="4" t="n">
-        <v>16.8</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="235">
@@ -8682,10 +8682,10 @@
         <v>162</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>13.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="236">
@@ -8717,10 +8717,10 @@
         <v>72</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="237">
@@ -8752,10 +8752,10 @@
         <v>258</v>
       </c>
       <c r="H237" s="4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I237" s="4" t="n">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="238">
@@ -8787,10 +8787,10 @@
         <v>120</v>
       </c>
       <c r="H238" s="4" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>19.8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="239">
@@ -8822,10 +8822,10 @@
         <v>264</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>26.4</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="240">
@@ -8857,10 +8857,10 @@
         <v>150</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>25.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="241">
@@ -8892,10 +8892,10 @@
         <v>600</v>
       </c>
       <c r="H241" s="4" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>60</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="242">
@@ -8927,10 +8927,10 @@
         <v>150</v>
       </c>
       <c r="H242" s="4" t="n">
-        <v>25</v>
+        <v>761</v>
       </c>
       <c r="I242" s="4" t="n">
-        <v>150</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="243">
@@ -8962,10 +8962,10 @@
         <v>12</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="244">
@@ -8997,10 +8997,10 @@
         <v>30</v>
       </c>
       <c r="H244" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I244" s="4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="245">
@@ -9032,10 +9032,10 @@
         <v>84</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="246">
@@ -9067,10 +9067,10 @@
         <v>12</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="247">
@@ -9137,10 +9137,10 @@
         <v>6</v>
       </c>
       <c r="H248" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="249">
@@ -9172,10 +9172,10 @@
         <v>438</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>43.8</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="250">
@@ -9207,10 +9207,10 @@
         <v>204</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>34.2</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="251">
@@ -9242,10 +9242,10 @@
         <v>96</v>
       </c>
       <c r="H251" s="4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="252">
@@ -9277,10 +9277,10 @@
         <v>24</v>
       </c>
       <c r="H252" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I252" s="4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="253">
@@ -9312,10 +9312,10 @@
         <v>180</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>15</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="254">
@@ -9347,10 +9347,10 @@
         <v>90</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>15</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="255">
@@ -9382,10 +9382,10 @@
         <v>84</v>
       </c>
       <c r="H255" s="4" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>10.8</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="256">
@@ -9452,10 +9452,10 @@
         <v>24</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I257" s="3" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="258">
@@ -9522,10 +9522,10 @@
         <v>12</v>
       </c>
       <c r="H259" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I259" s="4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="260">
@@ -9557,10 +9557,10 @@
         <v>30</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="261">
@@ -9592,10 +9592,10 @@
         <v>24</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="262">
@@ -9627,10 +9627,10 @@
         <v>66</v>
       </c>
       <c r="H262" s="4" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="I262" s="4" t="n">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="263">
@@ -9662,10 +9662,10 @@
         <v>48</v>
       </c>
       <c r="H263" s="4" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="I263" s="4" t="n">
-        <v>7.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="264">
@@ -9697,10 +9697,10 @@
         <v>72</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="265">
@@ -9732,10 +9732,10 @@
         <v>42</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I265" s="3" t="n">
-        <v>8.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="266">
@@ -9767,10 +9767,10 @@
         <v>30</v>
       </c>
       <c r="H266" s="4" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="I266" s="4" t="n">
-        <v>7.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="267">
@@ -9802,10 +9802,10 @@
         <v>24</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>4</v>
+        <v>12.2</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>24</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="268">
@@ -9837,10 +9837,10 @@
         <v>96</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="269">
@@ -9872,10 +9872,10 @@
         <v>36</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I269" s="3" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="270">
@@ -9907,10 +9907,10 @@
         <v>192</v>
       </c>
       <c r="H270" s="4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I270" s="4" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="271">
@@ -9942,10 +9942,10 @@
         <v>84</v>
       </c>
       <c r="H271" s="4" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="I271" s="4" t="n">
-        <v>13.8</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="272">
@@ -9977,10 +9977,10 @@
         <v>132</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I272" s="3" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="273">
@@ -10012,10 +10012,10 @@
         <v>60</v>
       </c>
       <c r="H273" s="3" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="I273" s="3" t="n">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="274">
@@ -10047,10 +10047,10 @@
         <v>318</v>
       </c>
       <c r="H274" s="4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I274" s="4" t="n">
-        <v>26.4</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="275">
@@ -10082,10 +10082,10 @@
         <v>144</v>
       </c>
       <c r="H275" s="4" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I275" s="4" t="n">
-        <v>24</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="276">
@@ -10117,10 +10117,10 @@
         <v>444</v>
       </c>
       <c r="H276" s="3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I276" s="3" t="n">
-        <v>37.2</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="277">
@@ -10152,10 +10152,10 @@
         <v>186</v>
       </c>
       <c r="H277" s="3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="I277" s="3" t="n">
-        <v>31.2</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="278">
@@ -10187,10 +10187,10 @@
         <v>348</v>
       </c>
       <c r="H278" s="4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I278" s="4" t="n">
-        <v>28.8</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="279">
@@ -10222,10 +10222,10 @@
         <v>108</v>
       </c>
       <c r="H279" s="4" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="I279" s="4" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="280">
@@ -10292,10 +10292,10 @@
         <v>48</v>
       </c>
       <c r="H281" s="4" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="I281" s="4" t="n">
-        <v>16.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="282">
@@ -10327,10 +10327,10 @@
         <v>72</v>
       </c>
       <c r="H282" s="4" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I282" s="4" t="n">
-        <v>12</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="283">
@@ -10362,10 +10362,10 @@
         <v>102</v>
       </c>
       <c r="H283" s="3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I283" s="3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="284">
@@ -10397,10 +10397,10 @@
         <v>42</v>
       </c>
       <c r="H284" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="I284" s="3" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="285">
@@ -10432,10 +10432,10 @@
         <v>240</v>
       </c>
       <c r="H285" s="4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I285" s="4" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="286">
@@ -10467,10 +10467,10 @@
         <v>96</v>
       </c>
       <c r="H286" s="4" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="I286" s="4" t="n">
-        <v>16.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="287">
@@ -10502,10 +10502,10 @@
         <v>480</v>
       </c>
       <c r="H287" s="3" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="I287" s="3" t="n">
-        <v>40.2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="288">
@@ -10537,10 +10537,10 @@
         <v>186</v>
       </c>
       <c r="H288" s="3" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="I288" s="3" t="n">
-        <v>31.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="289">
@@ -10572,10 +10572,10 @@
         <v>510</v>
       </c>
       <c r="H289" s="4" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I289" s="4" t="n">
-        <v>42.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="290">
@@ -10607,10 +10607,10 @@
         <v>228</v>
       </c>
       <c r="H290" s="4" t="n">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="I290" s="4" t="n">
-        <v>37.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="291">
@@ -10642,10 +10642,10 @@
         <v>66</v>
       </c>
       <c r="H291" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I291" s="3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="292">
@@ -10677,10 +10677,10 @@
         <v>168</v>
       </c>
       <c r="H292" s="4" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="I292" s="4" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="293">
@@ -10712,10 +10712,10 @@
         <v>78</v>
       </c>
       <c r="H293" s="4" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="I293" s="4" t="n">
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="294">
@@ -10747,10 +10747,10 @@
         <v>150</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="I294" s="3" t="n">
-        <v>12.6</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="295">
@@ -10782,10 +10782,10 @@
         <v>30</v>
       </c>
       <c r="H295" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="I295" s="3" t="n">
-        <v>7.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="296">
@@ -10817,10 +10817,10 @@
         <v>360</v>
       </c>
       <c r="H296" s="4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I296" s="4" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="297">
@@ -10852,10 +10852,10 @@
         <v>132</v>
       </c>
       <c r="H297" s="4" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I297" s="4" t="n">
-        <v>22.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="298">
@@ -10887,10 +10887,10 @@
         <v>240</v>
       </c>
       <c r="H298" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I298" s="3" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="299">
@@ -10922,10 +10922,10 @@
         <v>102</v>
       </c>
       <c r="H299" s="3" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="I299" s="3" t="n">
-        <v>16.8</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="300">
@@ -10957,10 +10957,10 @@
         <v>306</v>
       </c>
       <c r="H300" s="4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I300" s="4" t="n">
-        <v>25.2</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="301">
@@ -10992,10 +10992,10 @@
         <v>138</v>
       </c>
       <c r="H301" s="4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I301" s="4" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="302">
@@ -11027,10 +11027,10 @@
         <v>114</v>
       </c>
       <c r="H302" s="3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I302" s="3" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="303">
@@ -11062,10 +11062,10 @@
         <v>42</v>
       </c>
       <c r="H303" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I303" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="304">
@@ -11097,10 +11097,10 @@
         <v>312</v>
       </c>
       <c r="H304" s="4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I304" s="4" t="n">
-        <v>25.8</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="305">
@@ -11132,10 +11132,10 @@
         <v>228</v>
       </c>
       <c r="H305" s="4" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="I305" s="4" t="n">
-        <v>37.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="306">
@@ -11167,10 +11167,10 @@
         <v>498</v>
       </c>
       <c r="H306" s="3" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I306" s="3" t="n">
-        <v>41.4</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="307">
@@ -11202,10 +11202,10 @@
         <v>276</v>
       </c>
       <c r="H307" s="3" t="n">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I307" s="3" t="n">
-        <v>46.2</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="308">
@@ -11237,10 +11237,10 @@
         <v>3168</v>
       </c>
       <c r="H308" s="4" t="n">
-        <v>52.8</v>
+        <v>63.5</v>
       </c>
       <c r="I308" s="4" t="n">
-        <v>316.8</v>
+        <v>381</v>
       </c>
     </row>
     <row r="309">
@@ -11272,10 +11272,10 @@
         <v>882</v>
       </c>
       <c r="H309" s="4" t="n">
-        <v>29.4</v>
+        <v>40</v>
       </c>
       <c r="I309" s="4" t="n">
-        <v>176.4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="310">
@@ -11307,10 +11307,10 @@
         <v>36</v>
       </c>
       <c r="H310" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I310" s="3" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="311">
@@ -11342,10 +11342,10 @@
         <v>348</v>
       </c>
       <c r="H311" s="4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I311" s="4" t="n">
-        <v>28.8</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="312">
@@ -11377,10 +11377,10 @@
         <v>132</v>
       </c>
       <c r="H312" s="4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="I312" s="4" t="n">
-        <v>26.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="313">
@@ -11412,10 +11412,10 @@
         <v>114</v>
       </c>
       <c r="H313" s="3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I313" s="3" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="314">
@@ -11447,10 +11447,10 @@
         <v>36</v>
       </c>
       <c r="H314" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I314" s="3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="315">
@@ -11482,10 +11482,10 @@
         <v>120</v>
       </c>
       <c r="H315" s="4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="I315" s="4" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="316">
@@ -11517,10 +11517,10 @@
         <v>48</v>
       </c>
       <c r="H316" s="4" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I316" s="4" t="n">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="317">
@@ -11552,10 +11552,10 @@
         <v>318</v>
       </c>
       <c r="H317" s="3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I317" s="3" t="n">
-        <v>26.4</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="318">
@@ -11587,10 +11587,10 @@
         <v>150</v>
       </c>
       <c r="H318" s="3" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="I318" s="3" t="n">
-        <v>25.2</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="319">
@@ -11622,10 +11622,10 @@
         <v>90</v>
       </c>
       <c r="H319" s="4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="320">
@@ -11657,10 +11657,10 @@
         <v>168</v>
       </c>
       <c r="H320" s="3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I320" s="3" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="321">
@@ -11692,10 +11692,10 @@
         <v>72</v>
       </c>
       <c r="H321" s="3" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="I321" s="3" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="322">
@@ -11727,10 +11727,10 @@
         <v>108</v>
       </c>
       <c r="H322" s="4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I322" s="4" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="323">
@@ -11762,10 +11762,10 @@
         <v>12</v>
       </c>
       <c r="H323" s="3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I323" s="3" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="324">
@@ -11797,10 +11797,10 @@
         <v>420</v>
       </c>
       <c r="H324" s="4" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>46.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="325">
@@ -11832,10 +11832,10 @@
         <v>204</v>
       </c>
       <c r="H325" s="4" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="I325" s="4" t="n">
-        <v>34.2</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="326">
@@ -11867,10 +11867,10 @@
         <v>24</v>
       </c>
       <c r="H326" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I326" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="327">
@@ -11902,10 +11902,10 @@
         <v>30</v>
       </c>
       <c r="H327" s="3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I327" s="3" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="328">
@@ -11937,10 +11937,10 @@
         <v>6</v>
       </c>
       <c r="H328" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="329">
@@ -11972,10 +11972,10 @@
         <v>24</v>
       </c>
       <c r="H329" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="I329" s="3" t="n">
-        <v>7.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="330">
@@ -12007,10 +12007,10 @@
         <v>24</v>
       </c>
       <c r="H330" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I330" s="3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="331">
@@ -12042,10 +12042,10 @@
         <v>24</v>
       </c>
       <c r="H331" s="4" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="332">
@@ -12077,10 +12077,10 @@
         <v>66</v>
       </c>
       <c r="H332" s="3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I332" s="3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="333">
@@ -12112,10 +12112,10 @@
         <v>24</v>
       </c>
       <c r="H333" s="3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I333" s="3" t="n">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="334">
@@ -12147,10 +12147,10 @@
         <v>60</v>
       </c>
       <c r="H334" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I334" s="4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="335">
@@ -12182,10 +12182,10 @@
         <v>30</v>
       </c>
       <c r="H335" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I335" s="4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="336">
@@ -12217,10 +12217,10 @@
         <v>6</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I336" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="337">
@@ -12287,10 +12287,10 @@
         <v>18</v>
       </c>
       <c r="H338" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="339">
@@ -12322,10 +12322,10 @@
         <v>144</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="I339" s="3" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="340">
@@ -12357,10 +12357,10 @@
         <v>90</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I340" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="341">
@@ -12392,10 +12392,10 @@
         <v>96</v>
       </c>
       <c r="H341" s="4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I341" s="4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="342">
@@ -12427,10 +12427,10 @@
         <v>42</v>
       </c>
       <c r="H342" s="4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="I342" s="4" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="343">
@@ -12462,10 +12462,10 @@
         <v>528</v>
       </c>
       <c r="H343" s="3" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="I343" s="3" t="n">
-        <v>43.8</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="344">
@@ -12497,10 +12497,10 @@
         <v>264</v>
       </c>
       <c r="H344" s="3" t="n">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I344" s="3" t="n">
-        <v>43.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="345">
@@ -12532,10 +12532,10 @@
         <v>198</v>
       </c>
       <c r="H345" s="4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I345" s="4" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="346">
@@ -12567,10 +12567,10 @@
         <v>84</v>
       </c>
       <c r="H346" s="4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="I346" s="4" t="n">
-        <v>13.8</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="347">
@@ -12602,10 +12602,10 @@
         <v>336</v>
       </c>
       <c r="H347" s="3" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I347" s="3" t="n">
-        <v>28.2</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="348">
@@ -12637,10 +12637,10 @@
         <v>138</v>
       </c>
       <c r="H348" s="3" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="I348" s="3" t="n">
-        <v>22.8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="349">
@@ -12672,10 +12672,10 @@
         <v>204</v>
       </c>
       <c r="H349" s="4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="350">
@@ -12707,10 +12707,10 @@
         <v>30</v>
       </c>
       <c r="H350" s="4" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>15</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="351">
@@ -12742,10 +12742,10 @@
         <v>468</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I351" s="3" t="n">
-        <v>39</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="352">
@@ -12777,10 +12777,10 @@
         <v>186</v>
       </c>
       <c r="H352" s="3" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="I352" s="3" t="n">
-        <v>31.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="353">
@@ -12812,10 +12812,10 @@
         <v>120</v>
       </c>
       <c r="H353" s="4" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="I353" s="4" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="354">
@@ -12847,10 +12847,10 @@
         <v>30</v>
       </c>
       <c r="H354" s="4" t="n">
-        <v>5</v>
+        <v>152.2</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>30</v>
+        <v>913.2</v>
       </c>
     </row>
     <row r="355">
@@ -12882,10 +12882,10 @@
         <v>342</v>
       </c>
       <c r="H355" s="3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I355" s="3" t="n">
-        <v>28.8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="356">
@@ -12917,10 +12917,10 @@
         <v>132</v>
       </c>
       <c r="H356" s="3" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I356" s="3" t="n">
-        <v>22.2</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="357">
@@ -12952,10 +12952,10 @@
         <v>132</v>
       </c>
       <c r="H357" s="4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I357" s="4" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="358">
@@ -12987,10 +12987,10 @@
         <v>60</v>
       </c>
       <c r="H358" s="4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I358" s="4" t="n">
-        <v>10.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="359">
@@ -13022,10 +13022,10 @@
         <v>144</v>
       </c>
       <c r="H359" s="3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="I359" s="3" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="360">
@@ -13057,10 +13057,10 @@
         <v>48</v>
       </c>
       <c r="H360" s="3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I360" s="3" t="n">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="361">
@@ -13092,10 +13092,10 @@
         <v>96</v>
       </c>
       <c r="H361" s="4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I361" s="4" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="362">
@@ -13127,10 +13127,10 @@
         <v>282</v>
       </c>
       <c r="H362" s="3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I362" s="3" t="n">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="363">
@@ -13162,10 +13162,10 @@
         <v>96</v>
       </c>
       <c r="H363" s="3" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="I363" s="3" t="n">
-        <v>16.2</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="364">
@@ -13197,10 +13197,10 @@
         <v>36</v>
       </c>
       <c r="H364" s="4" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="I364" s="4" t="n">
-        <v>12</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="365">
@@ -13232,10 +13232,10 @@
         <v>144</v>
       </c>
       <c r="H365" s="3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="I365" s="3" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="366">
@@ -13267,10 +13267,10 @@
         <v>78</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="I366" s="3" t="n">
-        <v>13.2</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="367">
@@ -13302,10 +13302,10 @@
         <v>150</v>
       </c>
       <c r="H367" s="4" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="I367" s="4" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="368">
@@ -13337,10 +13337,10 @@
         <v>66</v>
       </c>
       <c r="H368" s="4" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I368" s="4" t="n">
-        <v>10.8</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="369">
@@ -13372,10 +13372,10 @@
         <v>192</v>
       </c>
       <c r="H369" s="3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I369" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="370">
@@ -13407,10 +13407,10 @@
         <v>84</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I370" s="3" t="n">
-        <v>16.8</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="371">
@@ -13442,10 +13442,10 @@
         <v>6</v>
       </c>
       <c r="H371" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I371" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="372">
@@ -13477,10 +13477,10 @@
         <v>234</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I372" s="3" t="n">
-        <v>19.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="373">
@@ -13512,10 +13512,10 @@
         <v>108</v>
       </c>
       <c r="H373" s="3" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I373" s="3" t="n">
-        <v>18</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="374">
@@ -13547,10 +13547,10 @@
         <v>90</v>
       </c>
       <c r="H374" s="4" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="I374" s="4" t="n">
-        <v>15</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="375">
@@ -13582,10 +13582,10 @@
         <v>330</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I375" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="376">
@@ -13617,10 +13617,10 @@
         <v>150</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="I376" s="3" t="n">
-        <v>30</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="377">
@@ -13652,10 +13652,10 @@
         <v>618</v>
       </c>
       <c r="H377" s="4" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="I377" s="4" t="n">
-        <v>51.6</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="378">
@@ -13687,10 +13687,10 @@
         <v>204</v>
       </c>
       <c r="H378" s="4" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="I378" s="4" t="n">
-        <v>40.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="379">
@@ -13722,10 +13722,10 @@
         <v>24</v>
       </c>
       <c r="H379" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I379" s="3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="380">
@@ -13792,10 +13792,10 @@
         <v>54</v>
       </c>
       <c r="H381" s="4" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="I381" s="4" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="382">
@@ -13827,10 +13827,10 @@
         <v>246</v>
       </c>
       <c r="H382" s="3" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="I382" s="3" t="n">
-        <v>20.4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="383">
@@ -13862,10 +13862,10 @@
         <v>102</v>
       </c>
       <c r="H383" s="3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="I383" s="3" t="n">
-        <v>20.4</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="384">
@@ -13897,10 +13897,10 @@
         <v>66</v>
       </c>
       <c r="H384" s="4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I384" s="4" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="385">
@@ -13932,10 +13932,10 @@
         <v>384</v>
       </c>
       <c r="H385" s="3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I385" s="3" t="n">
-        <v>31.8</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="386">
@@ -13967,10 +13967,10 @@
         <v>72</v>
       </c>
       <c r="H386" s="3" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="I386" s="3" t="n">
-        <v>24</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="387">
@@ -14002,10 +14002,10 @@
         <v>504</v>
       </c>
       <c r="H387" s="4" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I387" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="388">
@@ -14037,10 +14037,10 @@
         <v>168</v>
       </c>
       <c r="H388" s="4" t="n">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
       <c r="I388" s="4" t="n">
-        <v>28.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="389">
@@ -14072,10 +14072,10 @@
         <v>6</v>
       </c>
       <c r="H389" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I389" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="390">
@@ -14107,10 +14107,10 @@
         <v>102</v>
       </c>
       <c r="H390" s="4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="I390" s="4" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="391">
@@ -14142,10 +14142,10 @@
         <v>84</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I391" s="3" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="392">
@@ -14177,10 +14177,10 @@
         <v>42</v>
       </c>
       <c r="H392" s="3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I392" s="3" t="n">
-        <v>8.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="393">
@@ -14212,10 +14212,10 @@
         <v>24</v>
       </c>
       <c r="H393" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I393" s="4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="394">
@@ -14247,10 +14247,10 @@
         <v>30</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I394" s="3" t="n">
-        <v>30</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="395">
@@ -14282,10 +14282,10 @@
         <v>78</v>
       </c>
       <c r="H395" s="4" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="I395" s="4" t="n">
-        <v>11.4</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="396">
@@ -14317,10 +14317,10 @@
         <v>60</v>
       </c>
       <c r="H396" s="4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I396" s="4" t="n">
-        <v>10.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="397">
@@ -14352,10 +14352,10 @@
         <v>12</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I397" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="398">
@@ -14387,10 +14387,10 @@
         <v>18</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I398" s="3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="399">
@@ -14422,10 +14422,10 @@
         <v>54</v>
       </c>
       <c r="H399" s="4" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="I399" s="4" t="n">
-        <v>9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="400">
@@ -14457,10 +14457,10 @@
         <v>102</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>5.7</v>
+        <v>8.1</v>
       </c>
       <c r="I400" s="3" t="n">
-        <v>34.2</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="401">
@@ -14492,10 +14492,10 @@
         <v>12</v>
       </c>
       <c r="H401" s="4" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="I401" s="4" t="n">
-        <v>12</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="402">
@@ -14527,10 +14527,10 @@
         <v>18</v>
       </c>
       <c r="H402" s="3" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="I402" s="3" t="n">
-        <v>18</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="403">
@@ -14562,10 +14562,10 @@
         <v>18</v>
       </c>
       <c r="H403" s="4" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="I403" s="4" t="n">
-        <v>6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="404">
@@ -14597,10 +14597,10 @@
         <v>6</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I404" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="405">
@@ -14632,10 +14632,10 @@
         <v>90</v>
       </c>
       <c r="H405" s="3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I405" s="3" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="406">
@@ -14667,10 +14667,10 @@
         <v>30</v>
       </c>
       <c r="H406" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I406" s="3" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="407">
@@ -14702,10 +14702,10 @@
         <v>150</v>
       </c>
       <c r="H407" s="4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I407" s="4" t="n">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="408">
@@ -14737,10 +14737,10 @@
         <v>48</v>
       </c>
       <c r="H408" s="4" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="I408" s="4" t="n">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="409">
@@ -14772,10 +14772,10 @@
         <v>210</v>
       </c>
       <c r="H409" s="3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I409" s="3" t="n">
-        <v>17.4</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="410">
@@ -14807,10 +14807,10 @@
         <v>120</v>
       </c>
       <c r="H410" s="3" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="I410" s="3" t="n">
-        <v>19.8</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="411">
@@ -14842,10 +14842,10 @@
         <v>366</v>
       </c>
       <c r="H411" s="4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I411" s="4" t="n">
-        <v>30.6</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="412">
@@ -14877,10 +14877,10 @@
         <v>198</v>
       </c>
       <c r="H412" s="4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="I412" s="4" t="n">
-        <v>33</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="413">
@@ -14912,10 +14912,10 @@
         <v>84</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I413" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="414">
@@ -14947,10 +14947,10 @@
         <v>30</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="I414" s="3" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="415">
@@ -14982,10 +14982,10 @@
         <v>72</v>
       </c>
       <c r="H415" s="4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I415" s="4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="416">
@@ -15017,10 +15017,10 @@
         <v>42</v>
       </c>
       <c r="H416" s="4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I416" s="4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="417">
@@ -15052,10 +15052,10 @@
         <v>30</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="I417" s="3" t="n">
-        <v>10.2</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="418">
@@ -15087,10 +15087,10 @@
         <v>66</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I418" s="3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="419">
@@ -15122,10 +15122,10 @@
         <v>24</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="I419" s="3" t="n">
-        <v>7.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="420">
@@ -15157,10 +15157,10 @@
         <v>42</v>
       </c>
       <c r="H420" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I420" s="4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="421">
@@ -15192,10 +15192,10 @@
         <v>24</v>
       </c>
       <c r="H421" s="4" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I421" s="4" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="422">
@@ -15227,10 +15227,10 @@
         <v>156</v>
       </c>
       <c r="H422" s="3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I422" s="3" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="423">
@@ -15262,10 +15262,10 @@
         <v>12</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="I423" s="3" t="n">
-        <v>12</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="424">
@@ -15297,10 +15297,10 @@
         <v>276</v>
       </c>
       <c r="H424" s="4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I424" s="4" t="n">
-        <v>22.8</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="425">
@@ -15332,10 +15332,10 @@
         <v>96</v>
       </c>
       <c r="H425" s="4" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="I425" s="4" t="n">
-        <v>16.2</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="426">
@@ -15367,10 +15367,10 @@
         <v>192</v>
       </c>
       <c r="H426" s="3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I426" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="427">
@@ -15402,10 +15402,10 @@
         <v>84</v>
       </c>
       <c r="H427" s="3" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="I427" s="3" t="n">
-        <v>13.8</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="428">
@@ -15437,10 +15437,10 @@
         <v>72</v>
       </c>
       <c r="H428" s="4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I428" s="4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="429">
@@ -15472,10 +15472,10 @@
         <v>30</v>
       </c>
       <c r="H429" s="4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I429" s="4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="430">
@@ -15507,10 +15507,10 @@
         <v>192</v>
       </c>
       <c r="H430" s="3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I430" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="431">
@@ -15542,10 +15542,10 @@
         <v>72</v>
       </c>
       <c r="H431" s="3" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="I431" s="3" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="432">
@@ -15577,10 +15577,10 @@
         <v>198</v>
       </c>
       <c r="H432" s="4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I432" s="4" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="433">
@@ -15612,10 +15612,10 @@
         <v>156</v>
       </c>
       <c r="H433" s="3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I433" s="3" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="434">
@@ -15647,10 +15647,10 @@
         <v>72</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="I434" s="3" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="435">
@@ -15682,10 +15682,10 @@
         <v>318</v>
       </c>
       <c r="H435" s="4" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I435" s="4" t="n">
-        <v>26.4</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="436">
@@ -15717,10 +15717,10 @@
         <v>168</v>
       </c>
       <c r="H436" s="4" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="I436" s="4" t="n">
-        <v>28.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="437">
@@ -15752,10 +15752,10 @@
         <v>114</v>
       </c>
       <c r="H437" s="3" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="I437" s="3" t="n">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="438">
@@ -15787,10 +15787,10 @@
         <v>48</v>
       </c>
       <c r="H438" s="3" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="I438" s="3" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="439">
@@ -15822,10 +15822,10 @@
         <v>216</v>
       </c>
       <c r="H439" s="4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I439" s="4" t="n">
-        <v>18</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="440">
@@ -15857,10 +15857,10 @@
         <v>96</v>
       </c>
       <c r="H440" s="4" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="I440" s="4" t="n">
-        <v>16.2</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="441">
@@ -15892,10 +15892,10 @@
         <v>252</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I441" s="3" t="n">
-        <v>21</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="442">
@@ -15927,10 +15927,10 @@
         <v>126</v>
       </c>
       <c r="H442" s="3" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I442" s="3" t="n">
-        <v>21</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="443">
@@ -15962,10 +15962,10 @@
         <v>114</v>
       </c>
       <c r="H443" s="4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I443" s="4" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="444">
@@ -15997,10 +15997,10 @@
         <v>42</v>
       </c>
       <c r="H444" s="4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I444" s="4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="445">
@@ -16032,10 +16032,10 @@
         <v>588</v>
       </c>
       <c r="H445" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I445" s="3" t="n">
-        <v>49.2</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="446">
@@ -16067,10 +16067,10 @@
         <v>312</v>
       </c>
       <c r="H446" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I446" s="3" t="n">
-        <v>52.2</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="447">
@@ -16102,10 +16102,10 @@
         <v>294</v>
       </c>
       <c r="H447" s="4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I447" s="4" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="448">
@@ -16137,10 +16137,10 @@
         <v>114</v>
       </c>
       <c r="H448" s="4" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I448" s="4" t="n">
-        <v>19.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="449">
@@ -16172,10 +16172,10 @@
         <v>870</v>
       </c>
       <c r="H449" s="3" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="I449" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="450">
@@ -16207,10 +16207,10 @@
         <v>384</v>
       </c>
       <c r="H450" s="3" t="n">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="I450" s="3" t="n">
-        <v>64.2</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="451">
@@ -16242,10 +16242,10 @@
         <v>324</v>
       </c>
       <c r="H451" s="4" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="I451" s="4" t="n">
-        <v>36</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="452">
@@ -16277,10 +16277,10 @@
         <v>168</v>
       </c>
       <c r="H452" s="4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="I452" s="4" t="n">
-        <v>33.6</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="453">
@@ -16312,10 +16312,10 @@
         <v>84</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="I453" s="3" t="n">
-        <v>13.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="454">
@@ -16347,10 +16347,10 @@
         <v>48</v>
       </c>
       <c r="H454" s="4" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="I454" s="4" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="455">
@@ -16382,10 +16382,10 @@
         <v>144</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="I455" s="3" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="456">
@@ -16417,10 +16417,10 @@
         <v>42</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I456" s="3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="457">
@@ -16452,10 +16452,10 @@
         <v>78</v>
       </c>
       <c r="H457" s="4" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="I457" s="4" t="n">
-        <v>13.2</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="458">
@@ -16522,10 +16522,10 @@
         <v>12</v>
       </c>
       <c r="H459" s="4" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="I459" s="4" t="n">
-        <v>12</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="460">
@@ -16557,10 +16557,10 @@
         <v>42</v>
       </c>
       <c r="H460" s="4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I460" s="4" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="461">
@@ -16592,10 +16592,10 @@
         <v>54</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I461" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="462">
@@ -16627,10 +16627,10 @@
         <v>6</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I462" s="3" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="463">
@@ -16662,10 +16662,10 @@
         <v>282</v>
       </c>
       <c r="H463" s="4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I463" s="4" t="n">
-        <v>31.2</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="464">
@@ -16697,10 +16697,10 @@
         <v>132</v>
       </c>
       <c r="H464" s="4" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="I464" s="4" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="465">
@@ -16732,10 +16732,10 @@
         <v>96</v>
       </c>
       <c r="H465" s="3" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="I465" s="3" t="n">
-        <v>16.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="466">
@@ -16767,10 +16767,10 @@
         <v>102</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="I466" s="3" t="n">
-        <v>16.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="467">
@@ -16802,10 +16802,10 @@
         <v>66</v>
       </c>
       <c r="H467" s="4" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="I467" s="4" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="468">
@@ -16837,10 +16837,10 @@
         <v>54</v>
       </c>
       <c r="H468" s="4" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="I468" s="4" t="n">
-        <v>10.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="469">
@@ -16872,10 +16872,10 @@
         <v>18</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="I469" s="3" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="470">
@@ -16907,10 +16907,10 @@
         <v>12</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="I470" s="3" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="471">
@@ -16942,10 +16942,10 @@
         <v>294</v>
       </c>
       <c r="H471" s="4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I471" s="4" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="472">
@@ -16977,10 +16977,10 @@
         <v>144</v>
       </c>
       <c r="H472" s="4" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I472" s="4" t="n">
-        <v>24</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="473">
@@ -17012,10 +17012,10 @@
         <v>36</v>
       </c>
       <c r="H473" s="3" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="I473" s="3" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="474">
@@ -17047,10 +17047,10 @@
         <v>72</v>
       </c>
       <c r="H474" s="3" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I474" s="3" t="n">
-        <v>12</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="475">
@@ -17082,10 +17082,10 @@
         <v>36</v>
       </c>
       <c r="H475" s="4" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="I475" s="4" t="n">
-        <v>9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="476">
@@ -17117,10 +17117,10 @@
         <v>960</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>13.3</v>
+        <v>14.9</v>
       </c>
       <c r="I476" s="3" t="n">
-        <v>79.8</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="477">
@@ -17152,10 +17152,10 @@
         <v>414</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>13.8</v>
+        <v>16.9</v>
       </c>
       <c r="I477" s="3" t="n">
-        <v>82.8</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="478">
@@ -17187,10 +17187,10 @@
         <v>192</v>
       </c>
       <c r="H478" s="4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I478" s="4" t="n">
-        <v>21.6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="479">
@@ -17222,10 +17222,10 @@
         <v>120</v>
       </c>
       <c r="H479" s="4" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I479" s="4" t="n">
-        <v>40.2</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="480">
@@ -17257,10 +17257,10 @@
         <v>60</v>
       </c>
       <c r="H480" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I480" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="481">
@@ -17292,10 +17292,10 @@
         <v>24</v>
       </c>
       <c r="H481" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I481" s="3" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="482">
@@ -17327,10 +17327,10 @@
         <v>30</v>
       </c>
       <c r="H482" s="4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I482" s="4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="483">
@@ -17362,10 +17362,10 @@
         <v>42</v>
       </c>
       <c r="H483" s="4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I483" s="4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="484">
@@ -17397,10 +17397,10 @@
         <v>42</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I484" s="3" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="485">
@@ -17432,10 +17432,10 @@
         <v>24</v>
       </c>
       <c r="H485" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I485" s="3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="486">
@@ -17467,10 +17467,10 @@
         <v>6</v>
       </c>
       <c r="H486" s="4" t="n">
-        <v>1</v>
+        <v>30.4</v>
       </c>
       <c r="I486" s="4" t="n">
-        <v>6</v>
+        <v>182.4</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_grao_por_vendedor.xlsx
+++ b/relatorio_grao_por_vendedor.xlsx
@@ -527,10 +527,10 @@
         <v>24</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>121.8</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>730.8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -562,10 +562,10 @@
         <v>528</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>95.7</v>
+        <v>88</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>574.2</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4">
@@ -597,10 +597,10 @@
         <v>6</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -632,10 +632,10 @@
         <v>6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -667,10 +667,10 @@
         <v>6</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -807,10 +807,10 @@
         <v>6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2382,10 +2382,10 @@
         <v>6</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
@@ -2662,10 +2662,10 @@
         <v>12</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
@@ -4167,10 +4167,10 @@
         <v>6</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
@@ -4307,10 +4307,10 @@
         <v>6</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -4867,10 +4867,10 @@
         <v>12</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>10.1</v>
+        <v>2</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>60.6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127">
@@ -4902,10 +4902,10 @@
         <v>18</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128">
@@ -5322,10 +5322,10 @@
         <v>6</v>
       </c>
       <c r="H139" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140">
@@ -5497,10 +5497,10 @@
         <v>6</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
@@ -5672,10 +5672,10 @@
         <v>6</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150">
@@ -5812,10 +5812,10 @@
         <v>6</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154">
@@ -7072,10 +7072,10 @@
         <v>6</v>
       </c>
       <c r="H189" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190">
@@ -8227,10 +8227,10 @@
         <v>48</v>
       </c>
       <c r="H222" s="4" t="n">
-        <v>14.3</v>
+        <v>8</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>85.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="223">
@@ -8927,10 +8927,10 @@
         <v>150</v>
       </c>
       <c r="H242" s="4" t="n">
-        <v>761</v>
+        <v>25</v>
       </c>
       <c r="I242" s="4" t="n">
-        <v>4566</v>
+        <v>150</v>
       </c>
     </row>
     <row r="243">
@@ -9067,10 +9067,10 @@
         <v>12</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="247">
@@ -9137,10 +9137,10 @@
         <v>6</v>
       </c>
       <c r="H248" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="249">
@@ -9802,10 +9802,10 @@
         <v>24</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>12.2</v>
+        <v>4</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>73.2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="268">
@@ -11937,10 +11937,10 @@
         <v>6</v>
       </c>
       <c r="H328" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="329">
@@ -12217,10 +12217,10 @@
         <v>6</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I336" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="337">
@@ -12847,10 +12847,10 @@
         <v>30</v>
       </c>
       <c r="H354" s="4" t="n">
-        <v>152.2</v>
+        <v>5</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>913.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="355">
@@ -13442,10 +13442,10 @@
         <v>6</v>
       </c>
       <c r="H371" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I371" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="372">
@@ -14072,10 +14072,10 @@
         <v>6</v>
       </c>
       <c r="H389" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I389" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="390">
@@ -14247,10 +14247,10 @@
         <v>30</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I394" s="3" t="n">
-        <v>32.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="395">
@@ -14492,10 +14492,10 @@
         <v>12</v>
       </c>
       <c r="H401" s="4" t="n">
-        <v>10.1</v>
+        <v>2</v>
       </c>
       <c r="I401" s="4" t="n">
-        <v>60.6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="402">
@@ -14527,10 +14527,10 @@
         <v>18</v>
       </c>
       <c r="H402" s="3" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="I402" s="3" t="n">
-        <v>25.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="403">
@@ -14597,10 +14597,10 @@
         <v>6</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I404" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="405">
@@ -15262,10 +15262,10 @@
         <v>12</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="I423" s="3" t="n">
-        <v>25.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="424">
@@ -16522,10 +16522,10 @@
         <v>12</v>
       </c>
       <c r="H459" s="4" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="I459" s="4" t="n">
-        <v>25.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="460">
@@ -16627,10 +16627,10 @@
         <v>6</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I462" s="3" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="463">
@@ -17467,10 +17467,10 @@
         <v>6</v>
       </c>
       <c r="H486" s="4" t="n">
-        <v>30.4</v>
+        <v>1</v>
       </c>
       <c r="I486" s="4" t="n">
-        <v>182.4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
